--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0020.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0020.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Giảm DMG Thành Lũy Bình Minh</t>
+          <t>Giảm Sát Thương Lâu Đài Bình Minh</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Stage 4 Đòn Mid-air Attack: Tiêu Hao Thể Lực</t>
+          <t>Giai Đoạn 4 Đòn Mid-air Attack: Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực cho Trạng Thái Suspension trên không (mỗi giây)</t>
+          <t>Chi phí STA cho Trạng Thái Lơ Lửng trên không (mỗi giây)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 1 DMG Aemeath</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 1 Aemeath</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 2 DMG Aemeath</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 2 Aemeath</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 3 DMG Aemeath</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 3 Aemeath</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 4 DMG Aemeath</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 4 Aemeath</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Heavy Attack - Aemeath Nạp I Sát Thương</t>
+          <t>Đòn Tấn Công Mạnh - Aemeath Nạp I Sát Thương</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Heavy Attack - Aemeath Nạp II Sát Thương</t>
+          <t>Đòn Tấn Công Mạnh - Aemeath Nạp II Sát Thương</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Aemeath</t>
+          <t>Tấn Công Giữa Không - Sát Thương Aemeath</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>DMG Phản Đòn Né Tránh - Aemeath</t>
+          <t>Phản đòn né tránh - DMG Aemeath</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Heavy Attack - Aemeath Tiêu Hao Thể Lực</t>
+          <t>Đòn Tấn Công Mạnh - Aemeath Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu hao STA Aemeath</t>
+          <t>Tấn Công Giữa Không - Tiêu hao STA Aemeath</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sync Strike: Sát Thương Hợp Nhất Vũ Khí</t>
+          <t>Đòn Đồng Bộ: Armament Merge DMG</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sync Strike: Sát Thương Tiếng Gọi Dawn</t>
+          <t>Đòn Đồng Bộ: Call of Dawn DMG</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 1 DMG Mech</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 1 Mech</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 2 DMG Mech</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 2 Mech</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 3 DMG Mech</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 3 Mech</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 4 DMG Mech</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 4 Mech</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Nạp Cơ Khí I</t>
+          <t>Tấn Công Mạnh - Sát Thương Nạp Cơ Khí I</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Nạp Cơ Khí II</t>
+          <t>Tấn Công Mạnh - Sát Thương Nạp Cơ Khí II</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Máy Móc</t>
+          <t>Tấn Công Giữa Không - Sát Thương Máy Móc</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>DMG Phản Đòn Né Tránh - Mech</t>
+          <t>Phản đòn né tránh - DMG Cơ Giới</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Heavy Attack - Cơ Khí: Chi Phí Thể Lực</t>
+          <t>Tấn Công Mạnh - Cơ Khí: Chi Phí STA</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu Hao STA Máy Móc</t>
+          <t>Tấn Công Giữa Không - Tiêu Hao STA Máy Móc</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Chỉ Dụ Thiên Giáng: DMG Quá Tải</t>
+          <t>Thiên Lệnh Cú Đổ: Overdrive DMG</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Heavenfall Edict: DMG Kết Liền</t>
+          <t>Thiên Lệnh: Finale DMG</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thiên Lệnh Cú Đổ: Cooldown Quá Tải</t>
+          <t>Thiên Lệnh Cú Đổ: Overdrive Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thiên Lệnh: Thời Gian Cooldown Hoàn Mĩ</t>
+          <t>Thiên Lệnh: Finale Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thiên Lệnh Cú Đổ: Resonance Cost Quá Tải</t>
+          <t>Thiên Lệnh Cú Đổ: Chi Phí Cộng Hưởng Quá Tải</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Thiên Lệnh Cú Đổ: Tái Tạo Bản Giao Hưởng Quá Tải</t>
+          <t>Thiên Lệnh Cú Đổ: Overdrive Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Heavenfall Edict: Concerto Regen Kết Liền</t>
+          <t>Thiên Lệnh: Finale Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Songs Across the Universe DMG</t>
+          <t>DMG Khúc giao hưởng Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Debut of Meteoric Radiance DMG</t>
+          <t>Sát Thương Khúc Khải Hoàn Của Bản Concerto Ánh Sao Băng</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Seraphic Duet: Sát Thương Dư Âm</t>
+          <t>Song Tấu Seraphic: Encore DMG</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Seraphic Duet: Sát Thương Khúc Dạo Đầu</t>
+          <t>Song Tấu Seraphic: Overture DMG</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tune Rupture Response - Sát thương Starburst</t>
+          <t>Phản ứng Tune Rupture - DMG Starburst</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sát Thương Cộng Thêm Seraphic Duet (Mỗi Lần)</t>
+          <t>Sát Thương Cộng Thêm Song Tấu Seraphic (Mỗi Lần)</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{0} Tune AMP</t>
+          <t>{0} Điều chỉnh AMP</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{0} Tune AMP</t>
+          <t>{0} Điều chỉnh AMP</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Thời Gian Tồn Tại Ichor Blade</t>
+          <t>Thời Gian Tồn Tại Kiếm Dịch Huyết</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Cooldown Form Switch</t>
+          <t>Thời gian hồi Chuyển Hình Thái</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 4 của Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 4</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>BOOMY BOOM! DMG</t>
+          <t>BÙM BÙM! DMG</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>BIG BOOMY BOOM! DMG</t>
+          <t>NỔ TOANG TOANG! SÁT THƯƠNG!</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Soliskin to the Aid DMG</t>
+          <t>Soliskin hỗ trợ DMG!</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>BÙM BÙM! Cooldown chiêu</t>
+          <t>BÙM BÙM! Thời gian hồi chiêu</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Runic Outburst DMG</t>
+          <t>DMG Bùng Nổ Rune</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Runic Chain Whip DMG</t>
+          <t>DMG Roi Xích Rune</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Runic Soliskin DMG</t>
+          <t>DMG Da Solis Rune</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Forte Circuit - Học Bản Concerto Name Thật: Sát Thương</t>
+          <t>Forte Circuit - Học Bản Concerto Tên Thật: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Forte Circuit - Học Bản Concerto Name Thật: Thời Gian Cooldown</t>
+          <t>Forte Circuit - Học Bản Concerto Tên Thật: Thời gian hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Forte Circuit - Học Bản Concerto Name Thật: Hồi Phục</t>
+          <t>Forte Circuit - Học Bản Concerto Tên Thật: Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>DMG từ Mid-air Dodge Counter</t>
+          <t>Sát Thương Dodge Counter Tránh Trên Không</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Mid-air Dodge Counter</t>
+          <t>Tiêu Hao STA Dodge Counter Tránh Trên Không</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 3 DMG Hình Thức Diễn Xuất</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 3 Hình Thức Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 4 DMG Hình Thức Diễn Xuất</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 4 Hình Thức Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Dạng Nghệ Thuật Sân Khấu</t>
+          <t>Tấn Công Giữa Không - Sát Thương Dạng Nghệ Thuật Sân Khấu</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Dodge Phản Công - Sát Thương Hình Thái Diễn Xuất</t>
+          <t>Né Tránh Phản Công - Sát Thương Hình Thái Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 1 DMG Hình Thái Phân Rã</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 1 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 2 DMG Hình Thái Phân Rã</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 2 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Heavy Attack - Hình Thái Phân Rã Sát Thương</t>
+          <t>Đòn Tấn Công Mạnh - Hình Thái Phân Rã Sát Thương</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Sát Thương Hình Thái Phân Rã - Heavy Attack Trên Không</t>
+          <t>Sát Thương Hình Thái Phân Rã - Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Dodge Counter - Sát thương Hình Thái Phân Rã</t>
+          <t>Phản đòn né tránh - DMG Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Heavy Attack - Hình Thức Diễn Xuất Tiêu Hao STA</t>
+          <t>Tấn Công Mạnh - Hình Thức Diễn Xuất Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu Hao STA Dạng Nghệ Thuật Sân Khấu</t>
+          <t>Tấn Công Giữa Không - Tiêu Hao STA Dạng Nghệ Thuật Sân Khấu</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực dạng Phân Rã</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA dạng Phân Rã</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tiêu Hao STA Hình Thái Phân Rã - Heavy Attack Trên Không</t>
+          <t>Tiêu Hao STA Hình Thái Phân Rã - Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Bong Bóng Phantom - Sát Thương Hình Thái Diễn Xuất</t>
+          <t>Bong Bóng Ảo Ảnh - Sát Thương Hình Thái Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Beckon - Breakdown Form DMG</t>
+          <t>DMG Hóa Thân Triệu Hoán</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Hủy Diệt - Stage 1 DMG Hình Thái Suy Thoái</t>
+          <t>Hủy Diệt - Sát Thương Giai Đoạn 1 Hình Thái Suy Thoái</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Hủy Diệt - Stage 2 DMG Hình Thái Suy Thoái</t>
+          <t>Hủy Diệt - Sát Thương Giai Đoạn 2 Hình Thái Suy Thoái</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Bong Bóng Phantom - Thời Gian Cooldown Hình Thái Diễn Xuất</t>
+          <t>Bong Bóng Ảo Ảnh - Thời gian hồi Chiêu Hình Thái Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Mồi Ảo - Thời Gian Cooldown Hình Thức Diễn Xuất</t>
+          <t>Mồi Ảo - Thời gian hồi Chiêu Hình Thức Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Beckon - Breakdown Form Cooldown</t>
+          <t>Thời gian hồi Hóa Thân Triệu Hoán</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Hủy Diệt - Thời Gian Cooldown Hình Thái Suy Thoái</t>
+          <t>Hủy Diệt - Thời gian hồi Chiêu Hình Thái Suy Thoái</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Hồi Kết - Thời Gian Cooldown Hình Thái Diễn Xuất</t>
+          <t>Hồi Kết - Thời gian hồi Chiêu Hình Thái Diễn Xuất</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Hồi Kết - Thời Gian Cooldown Hình Thái Sụp Đổ</t>
+          <t>Hồi Kết - Thời gian hồi Chiêu Hình Thái Sụp Đổ</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>It's Been A While! DMG</t>
+          <t>Lâu rồi không gặp! SÁT THƯƠNG</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Sát Thương Knock Knock</t>
+          <t>Sát Thương Cốc Cốc</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khúc Giao Hưởng Knock Knock Hồi Phục</t>
+          <t>Khúc Giao Hưởng Cốc Cốc Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Sát Thương Tổ Erosion Mỗi Tíc Tắc</t>
+          <t>Sát Thương Tổ Xói Mòn Mỗi Tíc Tắc</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Dodge Counter - Decipher DMG</t>
+          <t>Phản đòn né tránh - DMG Giải Mã</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 1 DMG Tự Hiện Diện</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 1 Tự Hiện Diện</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Mảnh Băng Giá: Present Self</t>
+          <t>Tấn Công Mạnh - Sát Thương Mảnh Băng Giá: Present Self DMG</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Tự Hiện Tại</t>
+          <t>Tấn Công Giữa Không - Sát Thương Tự Hiện Tại</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Dodge Counter - Sát thương Present Self</t>
+          <t>Phản đòn né tránh - DMG Bản Ngã Hiện Tại</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Basic Attack - Tự Xưng Stage 1 Sát Thương</t>
+          <t>Basic Attack - Tự Xưng Giai Đoạn 1 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Basic Attack - Tự Xưng Stage 2 Sát Thương</t>
+          <t>Basic Attack - Tự Xưng Giai Đoạn 2 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Basic Attack - Tự Xưng Stage 3 Sát Thương</t>
+          <t>Basic Attack - Tự Xưng Giai Đoạn 3 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Basic Attack - Tự Xưng Stage 4 Sát Thương</t>
+          <t>Basic Attack - Tự Xưng Giai Đoạn 4 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Basic Attack - Tự Xưng Stage 5 Sát Thương</t>
+          <t>Basic Attack - Tự Xưng Giai Đoạn 5 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Foreclaimed Self</t>
+          <t>Tấn Công Mạnh - Sát Thương Bản Ngã Đã Định Trước</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bitterfrost: Tự Kết Tội Sát Thương</t>
+          <t>Đòn Tấn Công Mạnh - Bitterfrost: Foreclaimed Self DMG</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 1 DMG Tự Xác Định</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 1 Tự Xác Định</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 2 DMG Tự Xác Định</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 2 Tự Xác Định</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Dodge Counter - Sát thương Present Self</t>
+          <t>Phản đòn né tránh - DMG Bản Ngã Đã Định</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Frostblight: Sát Thương Ngọc Chém</t>
+          <t>Sương Độc: Jade Cleave DMG</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Frostblight: Sát Thương Rơi Cánh</t>
+          <t>Sương Độc: Petalfall DMG</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Foreclaiming: Inward Vision DMG</t>
+          <t>Nội Quan: Inward Vision DMG</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Foreclaiming: Blade Liberation DMG Cơ Bản</t>
+          <t>Giải Phóng Kiếm: Blade Liberation Base DMG</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Giải Phóng Kiếm: Blade Liberation cho mỗi Lưỡi Kiếm Snowforged</t>
+          <t>Tăng Sát Thương Giải Phóng Kiếm: Blade Liberation DMG Increase per Snowforged Blade</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Iai DMG (không có Frostharden Iai)</t>
+          <t>DMG Iai (không có Frostharden Iai)</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Resonance Skill - Hiện Thân: Cooldown</t>
+          <t>Resonance Skill - Hiện Thân: Hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Frostblight: Cooldown Ngọc Chém/Rơi Cánh</t>
+          <t>Sương Độc: Thời gian hồi Ngọc Chém/Rơi Cánh</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Nội Quan: Thời Gian Cooldown</t>
+          <t>Nội Quan: Inward Vision Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Giải Phóng Kiếm: Thời Gian Cooldown</t>
+          <t>Giải Phóng Kiếm: Blade Liberation Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Heavy Attack - Hiện Thân Tiêu Hao Thể Lực</t>
+          <t>Heavy Attack - Hiện Thân Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Heavy Attack - Mảnh Băng Sương: Chi Phí Thể Lực Khi Hiện Thân</t>
+          <t>Tấn Công Mạnh - Mảnh Băng Sương: Present Self STA Cost</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu Hao STA Tự Hiện Tại</t>
+          <t>Tấn Công Giữa Không - Tiêu Hao STA Tự Hiện Tại</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực mỗi giây khi nín thở</t>
+          <t>Chi phí STA mỗi giây khi nín thở</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bitterfrost: Tự Kết Tội Tiêu Hao Thể Lực</t>
+          <t>Đòn Tấn Công Mạnh - Bitterfrost: Foreclaimed Self STA Cost</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu Hao STA Stage 1 Tự Xác Định</t>
+          <t>Tấn Công Giữa Không - Tiêu Hao STA Giai Đoạn 1 Tự Xác Định</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Giai Đoạn Tự Xác Nhận Trước Tiêu Hao STA Cấp 2</t>
+          <t>Tấn Công Giữa Không - Giai Đoạn Tự Xác Nhận Trước Tiêu Hao STA Cấp 2</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Đòn Lao Xuống trên không - Chi phí Thể Lực Tự Gây</t>
+          <t>Đòn Lao Xuống trên không - Chi phí STA Tự Gây</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Iai Stance Tiêu Hao STA</t>
+          <t>Chi phí STA tư thế Iai</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Giải Phóng Kiếm: Resonance Cost</t>
+          <t>Giải Phóng Kiếm: Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Nội Quan: Hồi Phục Bản Giao Hưởng</t>
+          <t>Nội Quan: Inward Vision Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Giải Phóng Kiếm: Hồi Phục Bản Giao Hưởng</t>
+          <t>Giải Phóng Kiếm: Blade Liberation Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bitterfrost: Bản Concerto Tự Kết Tội Hồi Phục</t>
+          <t>Đòn Tấn Công Mạnh - Bitterfrost: Foreclaimed Self Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 1 DMG Hình Thái Phân Rã</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 1 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 2 DMG Hình Thái Phân Rã</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 2 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 3 DMG Hình Thái Phân Rã</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 3 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Stage 4 DMG Hình Thái Phân Rã</t>
+          <t>Tấn Công Giữa Không - Sát Thương Giai Đoạn 4 Hình Thái Phân Rã</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Hình Thái Phân Rã Tiêu Hao STA (Mỗi Giai Đoạn)</t>
+          <t>Tấn Công Giữa Không - Hình Thái Phân Rã Tiêu Hao STA (Mỗi Giai Đoạn)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực Foreclaimed Self</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA Bản Ngã Đã Định Trước</t>
         </is>
       </c>
     </row>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Thời Gian Final Bow</t>
+          <t>Thời Gian Cúi Chào Cuối</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tăng Attack {0}. Sau khi gây Sát Thương Basic Attack, người sử dụng nhận được {1} Spectro DMG Bonus trong {2} giây. Mỗi lần người sử dụng gây Tune Strain - Shifting lên mục tiêu, họ sẽ nhận được {3} DMG Amplification Basic Attack và Basic Attack của họ sẽ bỏ qua {4} Phòng Ngự của mục tiêu trong {5} giây.</t>
+          <t>Tăng ATK {0}. Sau khi gây Sát Thương Đòn Basic Attack, người sử dụng nhận được {1} Sát Thương Spectro Bonus trong {2} giây. Mỗi lần người sử dụng gây Tune Strain - Shifting lên mục tiêu, họ sẽ nhận được {3} Khuếch Đại Sát Thương Đòn Basic Attack và Đòn Basic Attack của họ sẽ bỏ qua {4} Phòng Ngự của mục tiêu trong {5} giây.</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tăng Hiệu Ứng Sát Thương Tất Cả Thuộc Tính lên {0}. Khi gây Tune Rupture - Shifting hoặc Fusion Burst, Sát Thương Resonance Liberation của người sử dụng sẽ bỏ qua {1} Phòng Ngự và {2} Fusion RES của mục tiêu trong {3} giây.</t>
+          <t>Tăng Hiệu Ứng Sát Thương Tất Cả Thuộc Tính lên {0}. Khi gây Tune Rupture - Shifting hoặc Fusion Burst, Sát Thương Resonance Liberation của người sử dụng sẽ bỏ qua {1} Phòng Ngự và {2} Kháng Fusion của mục tiêu trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công thêm {0}. Sử dụng Intro Skill hoặc Kỹ Năng Echo sẽ tăng {1} Sát Thương Kỹ Năng Echo trong {2} giây. Khi gây Sát Thương Kỹ Năng Echo, Aero DMG sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {4} giây.</t>
+          <t>Tăng ATK thêm {0}. Sử dụng Kỹ Năng Khởi Động hoặc Kỹ Năng Echo sẽ tăng {1} Sát Thương Kỹ Năng Echo trong {2} giây. Khi gây Sát Thương Kỹ Năng Echo, DMG Aero sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>ATK is increased by {0}. Sau khi người sử dụng gây Chafe Glacio, Glacio DMG được Khuếch Đại thêm {1}, và Sát Thương Resonance Liberation bỏ qua {2} Phòng Ngự của mục tiêu. Nếu người sử dụng là Resonator đang hoạt động trong đội, Sát Thương Chafe Glacio gây ra cho tất cả mục tiêu trong phạm vi nhất định sẽ được Khuếch Đại thêm {3} trong {4} giây. Hiệu ứng này có thể kích hoạt tối đa &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi {5} giây. Chỉ hiệu ứng mạnh nhất cùng tên được áp dụng.</t>
+          <t>ATK tăng {0}. Sau khi người sử dụng gây Chafe Glacio, Sát Thương Glacio được Khuếch Đại thêm {1}, và Sát Thương Resonance Liberation bỏ qua {2} Phòng Ngự của mục tiêu. Nếu người sử dụng là Resonator đang hoạt động trong đội, Sát Thương Chafe Glacio gây ra cho tất cả mục tiêu trong phạm vi nhất định sẽ được Khuếch Đại thêm {3} trong {4} giây. Hiệu ứng này có thể kích hoạt tối đa &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi {5} giây. Chỉ hiệu ứng mạnh nhất cùng tên được áp dụng.</t>
         </is>
       </c>
     </row>
@@ -14325,7 +14325,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tăng mức Độ Mistune Số tích lũy trên mục tiêu thông qua một số kỹ năng nhất định.</t>
+          <t>Scales up the Off-Tune Level accumulated on targets through certain skills.</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tune Break Boost làm tăng Sát thương Tune Break và Sát thương gây ra lên mục tiêu Bị Nhiễu</t>
+          <t>Tune Break Boost increases Tune Break DMG and the DMG dealt to Interfered targets</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       <c r="M214" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Feilian Beringal&lt;/color&gt;
-Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonators trong đội miễn nhiễm sát thương.</t>
+Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonator trong đội miễn nhiễm sát thương.</t>
         </is>
       </c>
     </row>
@@ -14523,8 +14523,8 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Inferno Rider&lt;/color&gt;
-Trong 15 giây sau khi đánh bại Inferno Rider, tất cả Resonators trong đội sẽ miễn nhiễm sát thương.</t>
+          <t>&lt;color=Highlight&gt;Kỵ Sĩ Hỏa Ngục&lt;/color&gt;
+Trong 15 giây sau khi đánh bại Kỵ Sĩ Hỏa Ngục, tất cả Resonator trong đội sẽ miễn nhiễm sát thương.</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-Sau khi đánh bại Sentry Construct, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.</t>
+Sau khi đánh bại Sentry Construct, tất cả Resonator trong đội sẽ miễn nhiễm sát thương trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Lampylumen Myriad&lt;/color&gt;
-Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonators trong đội sẽ miễn nhiễm sát thương.</t>
+Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonator trong đội sẽ miễn nhiễm sát thương.</t>
         </is>
       </c>
     </row>
@@ -14728,10 +14728,10 @@
       <c r="M218" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Feilian Beringal&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonators trong đội miễn nhiễm sát thương.
-- Feilian Beringal giảm 20% sát thương nhận vào. Khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, sát thương nhận vào tăng thêm 12.5% cho đến hết trận, tối đa 4 lần chồng chất.
-[Mở khóa ở Round 2] Hành vi của Feilian Beringal thay đổi. Sau khi tấn công, nó có thể triệu hồi Hoochiefs để tấn công tiếp.
-[Mở khóa ở Round 2] Sau khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, Feilian Beringal không thể triệu hồi Hoochiefs trong 15 giây.</t>
+- Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonator trong đội miễn nhiễm DMG.
+- Feilian Beringal giảm 20% DMG nhận vào. Khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, DMG nhận vào tăng thêm 12.5% cho đến hết trận, tối đa 4 lần chồng chất.
+[Mở khóa ở Vòng 2] Hành vi của Feilian Beringal thay đổi. Sau khi tấn công, nó có thể triệu hồi Hoochiefs để tấn công tiếp.
+[Mở khóa ở Vòng 2] Sau khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, Feilian Beringal không thể triệu hồi Hoochiefs trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -14799,10 +14799,10 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Inferno Rider&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Inferno Rider, tất cả Resonators trong đội sẽ miễn nhiễm sát thương.
-- Khi đòn tấn công của Inferno Rider trúng mục tiêu, nó sẽ gây hiệu ứng Thiêu Đốt, gây Fusion DMG liên tục. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Shield, sát thương sẽ giảm 90%.
-[Mở khóa ở Round 2] Inferno Rider liên tục gây Fusion DMG lên Resonators đang hoạt động gần nhất trong đội trên mặt đất. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Shield, sát thương sẽ giảm 90%.</t>
+          <t>&lt;color=Highlight&gt;Kỵ Sĩ Hỏa Ngục&lt;/color&gt;
+- Trong 15 giây sau khi đánh bại Kỵ Sĩ Hỏa Ngục, tất cả Resonator trong đội sẽ miễn nhiễm DMG.
+- Khi đòn tấn công của Kỵ Sĩ Hỏa Ngục trúng mục tiêu, nó sẽ gây hiệu ứng Thiêu Đốt, gây DMG Fusion liên tục. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Khiên, DMG sẽ giảm 90%.
+[Mở khóa ở Vòng 2] Kỵ Sĩ Hỏa Ngục liên tục gây DMG Fusion lên Resonator đang hoạt động gần nhất trong đội trên mặt đất. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Khiên, DMG sẽ giảm 90%.</t>
         </is>
       </c>
     </row>
@@ -14871,9 +14871,9 @@
       <c r="M220" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Sentry Construct, tất cả Resonators trong đội miễn nhiễm sát thương.
-- Khi Sentry Construct ở trên không, nó gây thêm 30% Sát Thương. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Concerto Vibrancy của Resonators tăng 50%.
-[Mở khóa ở Round 2] Hành vi của Sentry Construct thay đổi. Đòn phản công không còn hạ gục nó khỏi không trung.</t>
+- Trong 15 giây sau khi đánh bại Sentry Construct, tất cả Resonator trong đội miễn nhiễm DMG.
+- Khi Sentry Construct ở trên không, nó gây thêm 30% Sát Thương. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Sức Mạnh Rung Động của Resonator tăng 50%.
+[Mở khóa ở Vòng 2] Hành vi của Sentry Construct thay đổi. Đòn phản công không còn hạ gục nó khỏi không trung.</t>
         </is>
       </c>
     </row>
@@ -14942,9 +14942,9 @@
       <c r="M221" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Lampylumen Myriad&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonators trong đội sẽ miễn nhiễm sát thương.
-- Khi đòn tấn công của Lampylumen Myriad trúng mục tiêu, mục tiêu sẽ chịu thêm 5% sát thương, có thể chồng chất lên đến 10 lần. Khi Resonators không ở trên chiến trường, số lượt chồng chất sẽ giảm dần theo thời gian.
-[Mở khóa ở Round 2] Hiệu ứng tăng sát thương nhận vào của mục tiêu bị trúng đòn giờ có thể chồng chất lên đến 20 lần. Khi Lampylumen Myriad gây hiệu ứng Glacio Chafe, nó sẽ áp dụng thêm 1 lượt chồng chất của hiệu ứng này.</t>
+- Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonator trong đội sẽ miễn nhiễm DMG.
+- Khi đòn tấn công của Lampylumen Myriad trúng mục tiêu, mục tiêu sẽ chịu thêm 5% DMG, có thể chồng chất lên đến 10 lần. Khi Resonator không ở trên chiến trường, số lượt chồng chất sẽ giảm dần theo thời gian.
+[Mở khóa ở Vòng 2] Hiệu ứng tăng DMG nhận vào của mục tiêu bị trúng đòn giờ có thể chồng chất lên đến 20 lần. Khi Lampylumen Myriad gây hiệu ứng Glacio Chafe, nó sẽ áp dụng thêm 1 lượt chồng chất của hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -15014,8 +15014,8 @@
       <c r="M222" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Feilian Beringal&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonators trong đội miễn nhiễm sát thương.
-- Feilian Beringal giảm 20% sát thương nhận vào. Khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, sát thương nhận vào tăng thêm 12.5% cho đến hết trận, tối đa 4 lần chồng chất.
+- Trong 15 giây sau khi đánh bại Feilian Beringal, tất cả Resonator trong đội miễn nhiễm DMG.
+- Feilian Beringal giảm 20% DMG nhận vào. Khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, DMG nhận vào tăng thêm 12.5% cho đến hết trận, tối đa 4 lần chồng chất.
 - Hành vi của Feilian Beringal thay đổi. Sau khi tấn công, nó có thể triệu hồi Hoochiefs để tấn công tiếp.
 - Sau khi bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, Feilian Beringal không thể triệu hồi Hoochiefs trong 15 giây.</t>
         </is>
@@ -15085,10 +15085,10 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Inferno Rider&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Inferno Rider, tất cả Resonators trong đội đều miễn nhiễm sát thương.
-- Khi đòn tấn công của Inferno Rider trúng mục tiêu, nó sẽ gây hiệu ứng Bỏng, gây Fusion DMG liên tục. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Shield, sát thương sẽ giảm 90%.
-- Inferno Rider liên tục gây Fusion DMG lên Resonators đang hoạt động gần nhất trong đội khi ở trên mặt đất. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Shield, sát thương sẽ giảm 90%.</t>
+          <t>&lt;color=Highlight&gt;Kỵ Sĩ Hỏa Ngục&lt;/color&gt;
+- Trong 15 giây sau khi đánh bại Kỵ Sĩ Hỏa Ngục, tất cả Resonator trong đội đều miễn nhiễm DMG.
+- Khi đòn tấn công của Kỵ Sĩ Hỏa Ngục trúng mục tiêu, nó sẽ gây hiệu ứng Bỏng, gây DMG Fusion liên tục. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Khiên, DMG sẽ giảm 90%.
+- Kỵ Sĩ Hỏa Ngục liên tục gây DMG Fusion lên Resonator đang hoạt động gần nhất trong đội khi ở trên mặt đất. Nếu HP của mục tiêu trên 50% hoặc mục tiêu có Khiên, DMG sẽ giảm 90%.</t>
         </is>
       </c>
     </row>
@@ -15157,8 +15157,8 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-- Sau khi đánh bại Sentry Construct, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.
-- Khi Sentry Construct ở trên không, sát thương gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Concerto Vibrancy của Resonators tăng 50%.
+- Sau khi đánh bại Sentry Construct, tất cả Resonator trong đội sẽ miễn nhiễm DMG trong 15 giây.
+- Khi Sentry Construct ở trên không, DMG gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Sức Mạnh Rung Động của Resonator tăng 50%.
 - Hành vi của Sentry Construct thay đổi. Các đòn phản công không còn khiến nó bị hất ngã khi đang trên không.</t>
         </is>
       </c>
@@ -15229,10 +15229,10 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Lampylumen Myriad&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonators trong đội sẽ miễn nhiễm sát thương.
-- Khi đòn tấn công của Lampylumen Myriad trúng mục tiêu, mục tiêu sẽ chịu thêm 5% sát thương, có thể chồng chất lên đến 20 lần.
+- Trong 15 giây sau khi đánh bại Lampylumen Myriad, tất cả Resonator trong đội sẽ miễn nhiễm DMG.
+- Khi đòn tấn công của Lampylumen Myriad trúng mục tiêu, mục tiêu sẽ chịu thêm 5% DMG, có thể chồng chất lên đến 20 lần.
 - Khi Lampylumen Myriad gây hiệu ứng Glacio Chafe, nó sẽ áp dụng thêm 1 lượt chồng chất của hiệu ứng này.
-- Khi Resonators không ở trên chiến trường, số lượt chồng chất sẽ giảm dần theo thời gian.</t>
+- Khi Resonator không ở trên chiến trường, số lượt chồng chất sẽ giảm dần theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng sát thương nhận vào tăng thêm {0} trong {1} giây. Khi bị Aero Erosion, mỗi tầng làm tăng sát thương nhận vào thêm {2}, tối đa {3}.</t>
+          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng DMG nhận vào tăng thêm {0} trong {1} giây. Khi bị Aero Erosion, mỗi tầng làm tăng DMG nhận vào thêm {2}, tối đa {3}.</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị ảnh hưởng bởi Tune Rupture - Shifting hoặc Tune Strain - Shifting, tổng sát thương nhận vào tăng thêm {0}. Kẻ địch chịu thêm {1} sát thương Tune Rupture.</t>
+          <t>Khi kẻ địch bị ảnh hưởng bởi Tune Rupture - Shifting hoặc Tune Strain - Shifting, tổng DMG nhận vào tăng thêm {0}. Kẻ địch chịu thêm {1} DMG Tune Rupture.</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Khi Resonator nhận Shield, tổng Sát Thương gây ra tăng thêm {0} trong {1} giây, tối đa {2} lần.</t>
+          <t>Khi Resonator nhận Khiên, tổng Sát Thương gây ra tăng thêm {0} trong {1} giây, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Heavy Attack.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Basic Attack.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Kỹ Năng Echo. Mỗi khi một Resonators sử dụng Kỹ Năng Echo, tất cả Resonators trong đội gây thêm {1} Tổng Havoc DMG, tối đa {2}. Echo cùng tên từ cùng một Resonators không thể kích hoạt hiệu ứng này liên tục.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương từ Kỹ Năng Echo. Mỗi khi một Resonator sử dụng Kỹ Năng Echo, tất cả Resonator trong đội gây thêm {1} Tổng Sát Thương Havoc, tối đa {2}. Echo cùng tên từ cùng một Resonator không thể kích hoạt hiệu ứng này liên tục.</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng sát thương. Khi kích hoạt Resonance Liberation, Resonators trong đội nhận được {1} Tăng Sát Thương Resonance Skill trong {2} giây.</t>
+          <t>Resonator gây thêm {0} tổng DMG. Khi kích hoạt Resonance Liberation, các Resonator trong đội nhận được {1} Tăng Sát Thương Resonance Skill trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng sát thương. Khi kích hoạt Resonance Liberation, Resonators trong đội nhận được {1} Tăng Sát Thương Resonance Liberation trong {2} giây.</t>
+          <t>Resonator gây thêm {0} tổng DMG. Khi kích hoạt Resonance Liberation, các Resonator trong đội nhận được {1} Tăng Sát Thương Resonance Liberation trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng Sát Thương.</t>
+          <t>Resonator gây thêm {0} tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng Sát Thương.</t>
+          <t>Resonator gây thêm {0} tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng Sát Thương.</t>
+          <t>Resonator gây thêm {0} tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -16240,28 +16240,28 @@
 Khi Sigrika có ít nhất &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt;, chu kỳ Basic Attack của cô sẽ bắt đầu từ Stage 2.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Elucidated&lt;/color&gt;&lt;/size&gt;
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trên mặt đất để sử dụng &lt;color=Highlight&gt;Basic Attack - Elucidated&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Echo Skill DMG).
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trên mặt đất để sử dụng &lt;color=Highlight&gt;Basic Attack - Elucidated&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Echo Skill DMG).
 Rời khỏi trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt; sau khi sử dụng kỹ năng này.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Plunging Attack, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng Plunging Attack để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng Plunging Attack để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Decipher&lt;/color&gt;&lt;/size&gt;
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để sử dụng &lt;color=Highlight&gt;Dodge Counter - Decipher&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Echo Skill DMG).
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để sử dụng &lt;color=Highlight&gt;Dodge Counter - Decipher&lt;/color&gt; tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Echo Skill DMG).
 Rời khỏi trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt; sau khi sử dụng kỹ năng này.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công giữa không trung để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Mid-air Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công giữa không trung để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Mid-air Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16338,14 +16338,14 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;BOOMY BOOM!&lt;/color&gt;&lt;/size&gt;
 Tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;BOOMY BOOM!&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;BOOMY BOOM!&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;BIG BOOMY BOOM!&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; trên mặt đất để sử dụng &lt;color=Highlight&gt;BIG BOOMY BOOM!&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Vang Âm).
+Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill&lt;/color&gt; trên mặt đất để sử dụng &lt;color=Highlight&gt;BIG BOOMY BOOM!&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Vang Âm).
 Rời khỏi trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt; sau khi sử dụng kỹ năng này.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Soliskin to the Aid&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, với ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; trên mặt đất để sử dụng &lt;color=Highlight&gt;Soliskin to the Aid&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Vang Âm).
+Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt;, với ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill&lt;/color&gt; trên mặt đất để sử dụng &lt;color=Highlight&gt;Soliskin to the Aid&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Vang Âm).
 Rời khỏi trạng thái &lt;color=Highlight&gt;&lt;te href=141207&gt;Decipher&lt;/te&gt;&lt;/color&gt; sau khi sử dụng kỹ năng này.</t>
         </is>
       </c>
@@ -16642,7 +16642,7 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
 Hút mục tiêu xung quanh và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Echoes).
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Forte Circuit - Learn My True Name&lt;/color&gt;&lt;/size&gt;
-Khi &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt; đạt &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm}, nếu &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt; không trong Cooldown chiêu, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để thi triển &lt;color=Highlight&gt;Resonance Skill - BOOMY BOOM!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin to the Aid&lt;/color&gt;. &lt;color=Highlight&gt;Giữ Resonance Skill&lt;/color&gt; để tiêu hao toàn bộ &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt; và thi triển &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Echoes).
+Khi &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt; đạt &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm}, nếu &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt; không trong Thời gian hồi chiêu, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để thi triển &lt;color=Highlight&gt;Resonance Skill - BOOMY BOOM!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin to the Aid&lt;/color&gt;. &lt;color=Highlight&gt;Giữ Resonance Skill&lt;/color&gt; để tiêu hao toàn bộ &lt;color=Highlight&gt;&lt;te href=141202&gt;Full Stop&lt;/te&gt;&lt;/color&gt; và thi triển &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Kỹ Năng Echoes).
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Innate Gift?&lt;/color&gt;&lt;/size&gt;
 Sigrika có thể giữ tối đa &lt;SapTag=7&gt;{7}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng} &lt;color=Highlight&gt;Innate Gift?&lt;/color&gt;. Mỗi tầng tăng {8} Hiệu Ứng DMG Amplification cho &lt;color=Highlight&gt;Runic Outburst&lt;/color&gt;, &lt;color=Highlight&gt;Runic Chain Whip&lt;/color&gt;, &lt;color=Highlight&gt;Runic Soliskin&lt;/color&gt; và &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.
@@ -16938,16 +16938,16 @@
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; lâu hơn để tung &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cao hơn.
 Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt; tích năng lượng nhanh hơn. Sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Mech: Charged II&lt;/color&gt; hoặc Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Finale&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt;.
 Sát thương của kỹ năng này được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged I&lt;/color&gt; để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt; để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged I&lt;/color&gt; để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt; để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Aemeath&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Aemeath&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 4&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 4&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17052,13 +17052,13 @@
 Khi ở dạng Mech, Aemeath tự động thực hiện &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; khi sử dụng &lt;color=Highlight&gt;Form Switch&lt;/color&gt; trên không.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sync Strike: Armament Merge&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2, 3 &amp; 4&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Aemeath&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sync Strike: Armament Merge&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Chuyển sang dạng Mech sau khi sử dụng kỹ năng này. {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2, 3 &amp; 4&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Aemeath&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sync Strike: Armament Merge&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+Chuyển sang dạng Mech sau khi sử dụng kỹ năng này. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sync Strike: Call of Dawn&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Mech Stage 2, 3 &amp; 4&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Mech&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sync Strike: Call of Dawn&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Mech Stage 2, 3 &amp; 4&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Mech&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sync Strike: Call of Dawn&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Có thể sử dụng trên không.
-Chuyển sang dạng Aemeath sau khi sử dụng kỹ năng này. {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thực hiện &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
+Chuyển sang dạng Aemeath sau khi sử dụng kỹ năng này. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thực hiện &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Mech&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
@@ -17070,16 +17070,16 @@
 Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Mech: Charged II&lt;/color&gt; nạp nhanh hơn. Sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath: Charged II&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Mech: Charged II&lt;/color&gt; hoặc Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Finale&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt;.
 DMG của kỹ năng này được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 Có thể sử dụng trên không gần mặt đất.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Mech: Charged I&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Mech: Charged II&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Mech: Charged I&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Mech: Charged II&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Mech&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Plunging Attack, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Mech&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 4&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Mech Stage 4&lt;/color&gt;.
 Có thể sử dụng trên không gần mặt đất.</t>
         </is>
       </c>
@@ -17176,8 +17176,8 @@
 Sử dụng kỹ năng này sẽ kích hoạt các hiệu ứng sau:
 - Enter trạng thái &lt;color=Highlight&gt;&lt;te href=121002&gt;Stardust Resonance&lt;/te&gt;&lt;/color&gt; trong {0} giây.
 - Enter trạng thái &lt;color=Highlight&gt;&lt;te href=121003&gt;Heavenfall Edict: Unbound&lt;/te&gt;&lt;/color&gt; trong {1} giây.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi sử dụng kỹ năng này, thi triển &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi sử dụng kỹ năng này, thi triển &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
 &lt;color=Highlight&gt;&lt;te href=121007&gt;Seraphic Duet&lt;/te&gt;&lt;/color&gt; tiếp theo được sử dụng trong vòng {2} giây sau khi dùng kỹ năng này sẽ không tiêu hao &lt;color=Highlight&gt;&lt;te href=121012&gt;Rupturous Trail&lt;/te&gt;&lt;/color&gt;/&lt;color=Highlight&gt;&lt;te href=121013&gt;Fusion Trail&lt;/te&gt;&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Stardust Resonance&lt;/color&gt;&lt;/size&gt;
@@ -17189,7 +17189,7 @@
 Khi ở trạng thái &lt;color=Highlight&gt;Heavenfall Edict - Unbound&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=121005&gt;Resonance Rate&lt;/te&gt;&lt;/color&gt; đạt giới hạn, sẽ kích hoạt &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt;. &lt;color=Highlight&gt;&lt;te href=121001&gt;Instant Response&lt;/te&gt;&lt;/color&gt; sẽ bị loại bỏ khi trạng thái &lt;color=Highlight&gt;Heavenfall Edict - Unbound&lt;/color&gt; kết thúc.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavenfall Edict - Finale&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Heavenfall Edict: Finale&lt;/color&gt; khi đáp ứng đủ các điều kiện sau:
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Heavenfall Edict: Finale&lt;/color&gt; khi đáp ứng đủ các điều kiện sau:
 - Đang ở trạng thái &lt;color=Highlight&gt;&lt;te href=121003&gt;Heavenfall Edict: Unbound&lt;/te&gt;&lt;/color&gt;.
 - &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt; đạt giới hạn.
 - &lt;color=Highlight&gt;&lt;te href=121005&gt;Resonance Rate&lt;/te&gt;&lt;/color&gt; đạt giới hạn.
@@ -17420,15 +17420,15 @@
           <t>&lt;size=40&gt;&lt;color=Title&gt;Songs Across the Universe&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Kích hoạt kỹ năng này để bước vào trạng thái &lt;color=Highlight&gt;&lt;te href=121006&gt;Starlume Acceleration&lt;/te&gt;&lt;/color&gt; trong {0} giây.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; và kích hoạt Resonance Skill &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tự động tung ra &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; và kích hoạt Resonance Skill &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tự động tung ra &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Debut of Meteoric Radiance&lt;/color&gt;&lt;/size&gt;
 Ở dạng Mech, &lt;color=Highlight&gt;Songs Across the Universe&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Debut of Meteoric Radiance&lt;/color&gt;.
 Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Kích hoạt kỹ năng này sẽ mang lại trạng thái &lt;color=Highlight&gt;&lt;te href=121006&gt;Starlume Acceleration&lt;/te&gt;&lt;/color&gt; trong {0} giây.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; và kích hoạt Resonance Skill &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tự động tung ra &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack - Mech Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; và kích hoạt Resonance Skill &lt;color=Highlight&gt;Form Switch&lt;/color&gt; ngay sau khi kích hoạt kỹ năng này để tự động tung ra &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Starlume Acceleration&lt;/color&gt;&lt;/size&gt;
 Trong trạng thái &lt;color=Highlight&gt;Starlume Acceleration&lt;/color&gt;, kích hoạt Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; sẽ bổ sung hồi phục &lt;color=Highlight&gt;&lt;te href=121005&gt;Resonance Rate&lt;/te&gt;&lt;/color&gt;.
@@ -17637,7 +17637,7 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>Khi &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu đạt tối đa, Aemeath có thể sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; lên mục tiêu.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 Phản ứng với &lt;color=Highlight&gt;&lt;te href=100004&gt;Tune Rupture - Interfered&lt;/te&gt;&lt;/color&gt;: khi Resonators trong đội kích hoạt &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; lên mục tiêu và khiến chúng chịu &lt;color=Highlight&gt;&lt;te href=100004&gt;Tune Rupture - Interfered&lt;/te&gt;&lt;/color&gt;, Aemeath sẽ kích hoạt &lt;color=Highlight&gt;Tune Rupture Response - Starburst&lt;/color&gt;. Một mục tiêu chỉ có thể chịu sát thương từ kỹ năng này mỗi {0} giây một lần.</t>
         </is>
@@ -17787,7 +17787,7 @@
 Aemeath có thể chuyển đổi giữa hình dạng của bản thân và Cỗ Máy. Cỗ Máy kế thừa Stats của Aemeath và mở khóa các đòn tấn công mới.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sync Strike&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Stage 2, 3 &amp; 4&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Sync Strike&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chuyển đổi sang hình dạng khác.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Stage 2, 3 &amp; 4&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Sync Strike&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chuyển đổi sang hình dạng khác.</t>
         </is>
       </c>
     </row>
@@ -18419,7 +18419,7 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Present Self&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; liên tiếp hoặc giữ để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; liên tiếp hoặc giữ để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; áp dụng &lt;color=Highlight&gt;&lt;te href=850010&gt;Glacio Chafe&lt;/te&gt;&lt;/color&gt; 1 lần khi trúng đích.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;&lt;/size&gt;
@@ -18431,8 +18431,8 @@
 Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Present Self&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Foreclaimed Self&lt;/color&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Present Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self&lt;/color&gt;.
@@ -18440,8 +18440,8 @@
 &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 3, 4, and 5&lt;/color&gt; mỗi đòn áp dụng &lt;color=Highlight&gt;&lt;te href=850010&gt;Glacio Chafe&lt;/te&gt;&lt;/color&gt; 1 lần khi trúng đích.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Giữ Breath&lt;/color&gt;, liên tục tiêu hao STA. Khi thả &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc STA cạn kiệt, Hiyuki rời khỏi trạng thái &lt;color=Highlight&gt;Giữ Breath&lt;/color&gt; và lao tới, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 2&lt;/color&gt;.
-Nếu Hiyuki bị tấn công trong khoảng thời gian nhất định khi lao tới, sát thương đó sẽ bị vô hiệu hóa, làm choáng mục tiêu xung quanh và trở nên miễn nhiễm với gián đoạn trong một khoảng thời gian sau đó, đồng thời giảm 100% sát thương nhận vào. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi kích hoạt hiệu ứng này để chuyển thẳng vào &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 4&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Giữ Breath&lt;/color&gt;, liên tục tiêu hao STA. Khi thả &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc STA cạn kiệt, Hiyuki rời khỏi trạng thái &lt;color=Highlight&gt;Giữ Breath&lt;/color&gt; và lao tới, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 2&lt;/color&gt;.
+Nếu Hiyuki bị tấn công trong khoảng thời gian nhất định khi lao tới, sát thương đó sẽ bị vô hiệu hóa, làm choáng mục tiêu xung quanh và trở nên miễn nhiễm với gián đoạn trong một khoảng thời gian sau đó, đồng thời giảm 100% sát thương nhận vào. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi kích hoạt hiệu ứng này để chuyển thẳng vào &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;&lt;/size&gt;
 Khi &lt;color=Highlight&gt;&lt;te href=110804&gt;Whiteout Bitterfrost&lt;/te&gt;&lt;/color&gt; đầy, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;.
@@ -18458,8 +18458,8 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Foreclaimed Self&lt;/color&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter - Present Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Dodge Counter - Foreclaimed Self&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 3&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18540,17 +18540,17 @@
           <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Present Self&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 Sử dụng kỹ năng này sẽ tăng cường &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; tiếp theo, giúp hồi 100 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt; khi sử dụng. Chuyển đổi sang Resonator khác sẽ kết thúc hiệu ứng này.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Present Self&lt;/color&gt; sẽ được thay thế bởi &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt; và &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;:
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Frostblight: Jade Cleave&lt;/color&gt;&lt;/size&gt;
-Khi ở trên mặt đất, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để hút mục tiêu xung quanh và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời loại bỏ &lt;color=Highlight&gt;&lt;te href=110808&gt;Frostbind&lt;/te&gt;&lt;/color&gt; của mục tiêu.
-Skill này chia sẻ Cooldown chiêu với &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;.
+Khi ở trên mặt đất, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để hút mục tiêu xung quanh và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời loại bỏ &lt;color=Highlight&gt;&lt;te href=110808&gt;Frostbind&lt;/te&gt;&lt;/color&gt; của mục tiêu.
+Skill này chia sẻ Thời gian hồi chiêu với &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Frostblight: Petalfall&lt;/color&gt;&lt;/size&gt;
-Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để hút mục tiêu xung quanh và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời loại bỏ &lt;color=Highlight&gt;&lt;te href=110808&gt;Frostbind&lt;/te&gt;&lt;/color&gt; của mục tiêu.
-Skill này chia sẻ Cooldown chiêu với &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;.</t>
+Khi ở trên không, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để hút mục tiêu xung quanh và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời loại bỏ &lt;color=Highlight&gt;&lt;te href=110808&gt;Frostbind&lt;/te&gt;&lt;/color&gt; của mục tiêu.
+Skill này chia sẻ Thời gian hồi chiêu với &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18628,13 +18628,13 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Foreclaiming: Inward Vision&lt;/color&gt;&lt;/size&gt;
 &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt; sẽ khả dụng sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=110806&gt;Present Self&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để kích hoạt kỹ năng này, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Sau khi sử dụng, nhận 3 điểm &lt;color=Highlight&gt;&lt;te href=110803&gt;Frostharden Iai&lt;/te&gt;&lt;/color&gt;, trừ 300 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;. Sau đó, chuyển sang trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt; và hồi 50 điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=110806&gt;Present Self&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để kích hoạt kỹ năng này, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Sau khi sử dụng, nhận 3 điểm &lt;color=Highlight&gt;&lt;te href=110803&gt;Frostharden Iai&lt;/te&gt;&lt;/color&gt;, trừ 300 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;. Sau đó, chuyển sang trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt; và hồi 50 điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;.
 &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt; áp dụng 4 lớp &lt;color=Highlight&gt;&lt;te href=850010&gt;Glacio Chafe&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 Sử dụng &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt; không tiêu hao Resonance Energy.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Foreclaiming: Blade Liberation&lt;/color&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt;, có thể sử dụng &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt; theo các cách sau:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và thả ra để kích hoạt &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt;. Nếu Hiyuki có 3 điểm &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;, sẽ tiêu hao toàn bộ &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;. Ngược lại, lần kích hoạt này sẽ không tiêu hao &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; và thả ra để kích hoạt &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt;. Nếu Hiyuki có 3 điểm &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;, sẽ tiêu hao toàn bộ &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;. Ngược lại, lần kích hoạt này sẽ không tiêu hao &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt;.
 - Giữ &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để vào trạng thái nạp. Trong trạng thái này, tiêu hao 1 điểm &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt; theo chu kỳ. Thả &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt;. Nếu không tiêu hao điểm &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt; nào khi thả &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, Hiyuki sẽ tiếp tục nạp đòn tấn công và tự động kích hoạt kỹ năng sau một khoảng thời gian. &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt; cũng sẽ tự động kích hoạt khi &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt; cạn kiệt.
 Hiyuki gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Mỗi điểm &lt;color=Highlight&gt;&lt;te href=110805&gt;Snowforged Blade&lt;/te&gt;&lt;/color&gt; tiêu hao sẽ tăng Hệ Số Sát Thương của đòn tấn công này.
 Sử dụng kỹ năng sẽ tiêu hao 300 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;, đồng thời kết thúc trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt;.</t>
@@ -18845,8 +18845,8 @@
       <c r="M271" t="inlineStr">
         <is>
           <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Giải Resonance, và áp dụng &lt;color=Highlight&gt;&lt;te href=850010&gt;Glacio Chafe&lt;/te&gt;&lt;/color&gt; 1 lần khi trúng đòn.
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=110806&gt;Present Self&lt;/te&gt;&lt;/color&gt;, sử dụng kỹ năng này sẽ hồi phục 200 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng để thi triển &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng để thi triển &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 2&lt;/color&gt;.</t>
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=110806&gt;Present Self&lt;/te&gt;&lt;/color&gt;, sử dụng kỹ năng này sẽ hồi phục 200 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng để thi triển &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=110807&gt;Foreclaimed Self&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian sau khi sử dụng kỹ năng để thi triển &lt;color=Highlight&gt;Basic Attack - Foreclaimed Self Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18969,14 +18969,14 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Iai Stance&lt;/color&gt;&lt;/size&gt;
 Nếu Hiyuki có ít nhất 100 điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt;, thực hiện bất kỳ hành động nào sau đây sẽ khiến cô lướt lùi với chi phí STA và vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; sau khi sử dụng bất kỳ &lt;color=Highlight&gt;Normal Attacks - Foreclaimed Self&lt;/color&gt; nào khác ngoài &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;, &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;, &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Intro Skill - Frostedge&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; sau khi sử dụng bất kỳ &lt;color=Highlight&gt;Normal Attacks - Foreclaimed Self&lt;/color&gt; nào khác ngoài &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;, &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;, &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Intro Skill - Frostedge&lt;/color&gt;.
 - Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong một khoảng thời gian nhất định sau khi sử dụng &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt; hoặc &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;.
 Trong khi thực hiện các hành động trên, nếu có mục tiêu hợp lệ trong phạm vi và giữ nút di chuyển về phía trước, Hiyuki sẽ lướt ra sau lưng kẻ địch với chi phí STA và vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;.
 Hiyuki có thể vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; khi đang ở trên không. Khi vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, số lần Dodge trên không của Hiyuki sẽ được làm mới. &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; sẽ kết thúc nếu Hiyuki bị thay ra.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Iai&lt;/color&gt;&lt;/size&gt;
-Trong một khoảng thời gian nhất định sau khi vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; và tiêu hao 100 điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
-Nếu &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt; vẫn còn từ 100 điểm trở lên sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian nhất định để sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt; lại.
+Trong một khoảng thời gian nhất định sau khi vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; và tiêu hao 100 điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
+Nếu &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt; vẫn còn từ 100 điểm trở lên sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian nhất định để sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt; lại.
 Nếu Hiyuki bị tấn công bởi kẻ địch trong một khoảng thời gian nhất định khi đang sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, lượng sát thương này sẽ bị vô hiệu hóa và cô trở nên miễn nhiễm với gián đoạn trong một khoảng thời gian sau đó, đồng thời giảm 100% tất cả sát thương nhận vào.
 Mỗi lần sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, nếu Hiyuki có &lt;color=Highlight&gt;&lt;te href=110803&gt;Frostharden Iai&lt;/te&gt;&lt;/color&gt;, tiêu hao 1 điểm &lt;color=Highlight&gt;&lt;te href=110803&gt;Frostharden Iai&lt;/te&gt;&lt;/color&gt; để gây 3 lớp &lt;color=Highlight&gt;&lt;te href=850010&gt;Glacio Chafe&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu, và nhận 1 lớp &lt;color=Highlight&gt;&lt;te href=110804&gt;Whiteout Bitterfrost&lt;/te&gt;&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
@@ -19686,10 +19686,10 @@
 Hiyuki chuyển sang &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt;. Khi ở &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, các dạng kỹ năng mới sẽ được mở khóa.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Iai Stance&lt;/color&gt;&lt;/size&gt;
-Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong khi thực hiện một số đòn tấn công nhất định của &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt; để vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; với chi phí STA.
+Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong khi thực hiện một số đòn tấn công nhất định của &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt; để vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; với chi phí STA.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Iai&lt;/color&gt;&lt;/size&gt;
-Khi ở &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và chặn các đòn tấn công đến. Nếu Hiyuki có &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;, tiêu hao 1 tầng để tăng cường đòn tấn công này và nhận 1 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; để liên tục thực hiện đòn tấn công này.
+Khi ở &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và chặn các đòn tấn công đến. Nếu Hiyuki có &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;, tiêu hao 1 tầng để tăng cường đòn tấn công này và nhận 1 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; để liên tục thực hiện đòn tấn công này.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dedication&lt;/color&gt;&lt;/size&gt;
 Tài nguyên đặc biệt được sử dụng khi ở &lt;color=Highlight&gt;Present Self&lt;/color&gt;. Được tích lũy thông qua một số đòn tấn công nhất định và tiêu hao khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;.
@@ -19949,13 +19949,13 @@
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên không để thực hiện Đòn Hạ Cánh Holda Không, tiêu hao STA và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Stagecraft Form&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Stagecraft Form Stage 4&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Stagecraft Form Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Breakdown Form&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Có thể sử dụng giữa không trung.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Breakdown Form Stage 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack - Breakdown Form Stage 4&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Breakdown Form Stage 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack - Breakdown Form Stage 4&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20039,15 +20039,15 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Beckon - Breakdown Form&lt;/color&gt;&lt;/size&gt;
 Hút mục tiêu gần đó, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Skill này chia sẻ Cooldown chiêu với &lt;color=Highlight&gt;Banish - Breakdown Form&lt;/color&gt;.
+Skill này chia sẻ Thời gian hồi chiêu với &lt;color=Highlight&gt;Banish - Breakdown Form&lt;/color&gt;.
 Có thể sử dụng khi đang bay.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Banish - Breakdown Form&lt;/color&gt;&lt;/size&gt;
 Khi đang giữ &lt;color=Highlight&gt;&lt;te href=121101&gt;Dark Core&lt;/te&gt;&lt;/color&gt;, thay thế &lt;color=Highlight&gt;Beckon - Breakdown Form&lt;/color&gt; bằng &lt;color=Highlight&gt;Banish - Breakdown Form&lt;/color&gt;.
-Sử dụng &lt;color=Highlight&gt;Banish - Breakdown Form Stage 1&lt;/color&gt; để hút mục tiêu gần đó, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau đó để kích hoạt &lt;color=Highlight&gt;Banish - Breakdown Form Stage 2&lt;/color&gt;.
+Sử dụng &lt;color=Highlight&gt;Banish - Breakdown Form Stage 1&lt;/color&gt; để hút mục tiêu gần đó, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; ngay sau đó để kích hoạt &lt;color=Highlight&gt;Banish - Breakdown Form Stage 2&lt;/color&gt;.
 &lt;color=Highlight&gt;Banish - Breakdown Form Stage 2&lt;/color&gt; tiêu thụ toàn bộ &lt;color=Highlight&gt;&lt;te href=121101&gt;Dark Cores&lt;/te&gt;&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Với mỗi &lt;color=Highlight&gt;&lt;te href=121101&gt;Dark Core&lt;/te&gt;&lt;/color&gt; tiêu thụ, Hệ Số Sát Thương của đòn tấn công sẽ tăng thêm {0}.
 Skill này gây Sát Thương Resonance Liberation.
-Skill này chia sẻ Cooldown chiêu với &lt;color=Highlight&gt;Beckon - Breakdown Form&lt;/color&gt;.
+Skill này chia sẻ Thời gian hồi chiêu với &lt;color=Highlight&gt;Beckon - Breakdown Form&lt;/color&gt;.
 Có thể sử dụng khi đang bay.</t>
         </is>
       </c>
@@ -20352,7 +20352,7 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;It's Been A While!&lt;/color&gt;&lt;/size&gt;
 Available ở &lt;color=Highlight&gt;Stagecraft Form&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thi triển kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Stagecraft Form Stage 4&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thi triển kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Stagecraft Form Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Knock Knock&lt;/color&gt;&lt;/size&gt;
 Available ở &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
@@ -22175,7 +22175,7 @@
       <c r="M313" t="inlineStr">
         <is>
           <t>Khi &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu đạt tối đa, Sigrika có thể sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; lên mục tiêu.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;&lt;te href=100001&gt;Tune Break&lt;/te&gt;&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22380,7 +22380,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Resonators gây thêm {0} tổng Sát Thương.</t>
+          <t>Resonator gây thêm {0} tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Các Resonators Demo sẽ kế thừa các nút Chuỗi Resonance từ Resonators của ngươi.</t>
+          <t>Các Resonator Demo sẽ kế thừa các nút Resonance Chain từ Resonator của ngươi.</t>
         </is>
       </c>
     </row>
@@ -22512,7 +22512,7 @@
       <c r="M318" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Hyvatia&lt;/color&gt;
-Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonators trong đội đều miễn nhiễm sát thương.</t>
+Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonator trong đội đều miễn nhiễm sát thương.</t>
         </is>
       </c>
     </row>
@@ -22579,7 +22579,7 @@
       <c r="M319" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-Sau khi đánh bại Sentry Construct, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.</t>
+Sau khi đánh bại Sentry Construct, tất cả Resonator trong đội sẽ miễn nhiễm sát thương trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -22650,11 +22650,11 @@
       <c r="M320" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Hyvatia&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonators trong đội đều miễn nhiễm sát thương.
-- Giảm trừ Concerto Vibrancy mà Hyvatia phải chịu giảm 25%. Khi Hyvatia ở trên không, mức giảm trừ này tăng thêm 50%.
-- Khi Resonators kích hoạt phản đòn thành công, Hyvatia tích lũy 30% &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; tối đa. Hiệu ứng này có Cooldown 20 giây.
-- Khi Hyvatia chịu sát thương Vỡ Tần Số, Concerto Vibrancy của nó giảm 8%. Hiệu ứng này có Cooldown 5 giây.
-[Mở khóa ở Round 2] Thời gian Bất Động của Hyvatia giảm 20%.</t>
+- Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonator trong đội đều miễn nhiễm DMG.
+- Giảm trừ Sức Mạnh Rung Động mà Hyvatia phải chịu giảm 25%. Khi Hyvatia ở trên không, mức giảm trừ này tăng thêm 50%.
+- Khi Resonator kích hoạt phản đòn thành công, Hyvatia tích lũy 30% &lt;color=Highlight&gt;Mức Độ Lệch Tần Số&lt;/color&gt; tối đa. Hiệu ứng này có thời gian hồi 20 giây.
+- Khi Hyvatia chịu DMG Vỡ Tần Số, Sức Mạnh Rung Động của nó giảm 8%. Hiệu ứng này có thời gian hồi 5 giây.
+[Mở khóa ở Vòng 2] Thời gian Bất Động của Hyvatia giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -22723,9 +22723,9 @@
       <c r="M321" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-- Sau khi đánh bại Sentry Construct, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.
-- Mức giảm Concerto Vibrancy mà Sentry Construct phải chịu giảm 25%. Khi Sentry Construct ở trên không, sát thương gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Concerto Vibrancy của Resonators tăng 50%.
-[Mở khóa ở Round 2] Tấn Công của Sentry Construct tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Bị hóa đá sẽ xóa toàn bộ cộng dồn và tạm dừng hiệu ứng.</t>
+- Sau khi đánh bại Sentry Construct, tất cả Resonator trong đội sẽ miễn nhiễm DMG trong 15 giây.
+- Mức giảm Sức Mạnh Rung Động mà Sentry Construct phải chịu giảm 25%. Khi Sentry Construct ở trên không, DMG gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Sức Mạnh Rung Động của Resonator tăng 50%.
+[Mở khóa ở Vòng 2] ATK của Sentry Construct tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Bị hóa đá sẽ xóa toàn bộ cộng dồn và tạm dừng hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -22796,10 +22796,10 @@
       <c r="M322" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Hyvatia&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonators trong đội đều miễn nhiễm sát thương.
-- Giảm trừ Concerto Vibrancy mà Hyvatia phải chịu giảm 25%. Khi Hyvatia ở trên không, mức giảm trừ này tăng thêm 50%.
-- Khi Resonators kích hoạt phản đòn thành công, Hyvatia tích lũy 30% &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; tối đa. Hiệu ứng này có Cooldown 20 giây.
-- Khi Hyvatia chịu sát thương Vỡ Tần Số, Concerto Vibrancy của nó giảm 8%. Hiệu ứng này có Cooldown 5 giây.
+- Trong 15 giây sau khi đánh bại Hyvatia, tất cả Resonator trong đội đều miễn nhiễm DMG.
+- Giảm trừ Sức Mạnh Rung Động mà Hyvatia phải chịu giảm 25%. Khi Hyvatia ở trên không, mức giảm trừ này tăng thêm 50%.
+- Khi Resonator kích hoạt phản đòn thành công, Hyvatia tích lũy 30% &lt;color=Highlight&gt;Mức Độ Lệch Tần Số&lt;/color&gt; tối đa. Hiệu ứng này có thời gian hồi 20 giây.
+- Khi Hyvatia chịu DMG Vỡ Tần Số, Sức Mạnh Rung Động của nó giảm 8%. Hiệu ứng này có thời gian hồi 5 giây.
 - Thời gian Bất Động của Hyvatia giảm 20%.</t>
         </is>
       </c>
@@ -22869,9 +22869,9 @@
       <c r="M323" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sentry Construct&lt;/color&gt;
-- Sau khi đánh bại Sentry Construct, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.
-- Mức giảm Concerto Vibrancy mà Sentry Construct phải chịu giảm 25%. Khi Sentry Construct ở trên không, sát thương gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Concerto Vibrancy của Resonators tăng 50%.
-- Tấn Công của Sentry Construct tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Bị hóa đá sẽ xóa toàn bộ cộng dồn và tạm dừng hiệu ứng.</t>
+- Sau khi đánh bại Sentry Construct, tất cả Resonator trong đội sẽ miễn nhiễm DMG trong 15 giây.
+- Mức giảm Sức Mạnh Rung Động mà Sentry Construct phải chịu giảm 25%. Khi Sentry Construct ở trên không, DMG gây ra tăng 30%. Nếu bị ảnh hưởng bởi &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tunability - Shifting&lt;/color&gt;, tỷ lệ giảm Sức Mạnh Rung Động của Resonator tăng 50%.
+- ATK của Sentry Construct tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Bị hóa đá sẽ xóa toàn bộ cộng dồn và tạm dừng hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -22937,8 +22937,8 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị ảnh hưởng bởi Tune Rupture - Shifting hoặc Tune Rupture - Interfered, tổng sát thương nhận vào tăng thêm {0}. Kẻ địch chịu thêm {1} sát thương Tune Rupture.
-Khi kẻ địch bị ảnh hưởng bởi Tune Strain - Shifting hoặc Tune Strain - Interfered, tổng sát thương nhận vào tăng thêm {2}.</t>
+          <t>Khi kẻ địch bị ảnh hưởng bởi Tune Rupture - Shifting hoặc Tune Rupture - Interfered, tổng DMG nhận vào tăng thêm {0}. Kẻ địch chịu thêm {1} DMG Tune Rupture.
+Khi kẻ địch bị ảnh hưởng bởi Tune Strain - Shifting hoặc Tune Strain - Interfered, tổng DMG nhận vào tăng thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng sát thương nhận vào tăng thêm {0} trong {1} giây. Khi bị Fusion Burst, tổng sát thương nhận vào tăng thêm {2}.</t>
+          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng DMG nhận vào tăng thêm {0} trong {1} giây. Khi bị Fusion Burst, tổng DMG nhận vào tăng thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Tổng sát thương Skill Echo tăng {0}. Tổng Fusion DMG tăng {1}. Tổng sát thương Heavy Attack tăng {2}.</t>
+          <t>Tổng DMG Kỹ năng Echo tăng {0}. Tổng DMG Fusion tăng {1}. Tổng DMG Đòn Tấn Công Mạnh tăng {2}.</t>
         </is>
       </c>
     </row>
@@ -23135,9 +23135,9 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Instant Response&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; sẽ tích đủ năng lượng nhanh hơn.
-- Khi đồng thời ở trạng thái &lt;color=Highlight&gt;Instant Response&lt;/color&gt; và &lt;color=Highlight&gt;Heavenfall Edict: Unbound&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath Charged II&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack - Mech Charged II&lt;/color&gt; sẽ hồi phục {0} điểm &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.
-- Nếu Inherent Skill &lt;color=Highlight&gt;Before Tất cả Sounds&lt;/color&gt; được kích hoạt, khi ở trạng thái &lt;color=Highlight&gt;Instant Response&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; sẽ nhận thêm {2} DMG Amplification.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Phản Ứng Tức Thì&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; sẽ tích đủ năng lượng nhanh hơn.
+- Khi đồng thời ở trạng thái &lt;color=Highlight&gt;Phản Ứng Tức Thì&lt;/color&gt; và &lt;color=Highlight&gt;Thiên Lệnh Sa Đọa: Vô Ngại&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath Tích Năng II&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack - Mech Tích Năng II&lt;/color&gt; sẽ hồi phục {0} điểm &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.
+- Nếu Kỹ Năng Nội Tại &lt;color=Highlight&gt;Trước Mọi Âm Thanh&lt;/color&gt; được kích hoạt, khi ở trạng thái &lt;color=Highlight&gt;Phản Ứng Tức Thì&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Aemeath&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Mech&lt;/color&gt; sẽ nhận thêm {2} Khuếch Đại Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -23204,9 +23204,9 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Stardust Resonance&lt;/color&gt; tăng cường hiệu ứng của Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; dựa trên &lt;color=Highlight&gt;Resonance Mode&lt;/color&gt; hiện tại của Aemeath:
-- Khi ở &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, giờ đây có thể kích hoạt tối đa {0} lần &lt;color=Highlight&gt;Tune Rupture DMG&lt;/color&gt; trong Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt;.
-- Khi ở &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, Hệ Số Sát Thương của &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; được kích hoạt chủ động trong Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; đối với mục tiêu chính của &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; sẽ tăng thêm {1}. Hiệu ứng tăng Hệ Số Sát Thương này có thể chồng chất với hiệu ứng từ &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Cộng Hưởng Sao Băng&lt;/color&gt; tăng cường hiệu ứng của Resonance Skill &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt; dựa trên &lt;color=Highlight&gt;Chế Độ Cộng Hưởng&lt;/color&gt; hiện tại của Aemeath:
+- Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Đoạn Tune Vỡ&lt;/color&gt;, giờ đây có thể kích hoạt tối đa {0} lần &lt;color=Highlight&gt;Sát Thương Đoạn Tune Vỡ&lt;/color&gt; trong Resonance Skill &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt;.
+- Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Fusion Burst&lt;/color&gt;, Hệ Số Sát Thương của &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; được kích hoạt chủ động trong Resonance Skill &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt; đối với mục tiêu chính của &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; sẽ tăng thêm {1}. Hiệu ứng tăng Hệ Số Sát Thương này có thể chồng chất với hiệu ứng từ &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23342,11 +23342,11 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; bị giới hạn ở mức {0} điểm.
-- Gây sát thương bằng &lt;color=Highlight&gt;Basic Attack - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Mech&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Mech&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter - Mech&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Sync Strike: Armament Merge&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Sync Strike: Call of Dawn&lt;/color&gt; sẽ phục hồi &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.
-- Sử dụng Intro Skill &lt;color=Highlight&gt;Songs Across the Universe&lt;/color&gt; hoặc &lt;color=Highlight&gt;Debut of Meteoric Radiance&lt;/color&gt; sẽ phục hồi {1} điểm &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.
-- Sử dụng Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; sẽ phục hồi {2} điểm &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.
-- Khi đồng thời ở trạng thái &lt;color=Highlight&gt;Instant Response&lt;/color&gt; và &lt;color=Highlight&gt;Heavenfall Edict: Unbound&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Heavy Attack - Aemeath Charged II&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack - Mech Charged II&lt;/color&gt; sẽ phục hồi {3} điểm &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; bị giới hạn ở mức {0} điểm.
+- Gây sát thương bằng &lt;color=Highlight&gt;Đòn Basic Attack - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Mid-air Attack - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter Tránh - Aemeath&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack - Mech&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Mid-air Attack - Mech&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter Tránh - Mech&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Đòn Đồng Bộ: Hợp Nhất Vũ Khí&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Đòn Đồng Bộ: Tiếng Gọi Bình Minh&lt;/color&gt; sẽ phục hồi &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.
+- Sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Khúc Ca Vượt Vũ Trụ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Khúc Khải Huyền Quang&lt;/color&gt; sẽ phục hồi {1} điểm &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.
+- Sử dụng Resonance Liberation &lt;color=Highlight&gt;Thiên Lệnh: Siêu Tải&lt;/color&gt; sẽ phục hồi {2} điểm &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.
+- Khi đồng thời ở trạng thái &lt;color=Highlight&gt;Phản Ứng Tức Thì&lt;/color&gt; và &lt;color=Highlight&gt;Thiên Lệnh: Không Giới Hạn&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Aemeath Nạp II&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Heavy Attack - Mech Nạp II&lt;/color&gt; sẽ phục hồi {3} điểm &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23414,10 +23414,10 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; bị giới hạn ở {0} điểm.
-- Kích hoạt Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; phục hồi {1} điểm &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.
-- Kích hoạt Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; phục hồi {2} điểm &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.
-- Khi ở trạng thái &lt;color=Highlight&gt;Starlume Acceleration&lt;/color&gt;, kích hoạt Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; sẽ phục hồi thêm {3} điểm &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Tần Số Cộng Hưởng&lt;/color&gt; bị giới hạn ở {0} điểm.
+- Kích hoạt Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; phục hồi {1} điểm &lt;color=Highlight&gt;Tần Số Cộng Hưởng&lt;/color&gt;.
+- Kích hoạt Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; phục hồi {2} điểm &lt;color=Highlight&gt;Tần Số Cộng Hưởng&lt;/color&gt;.
+- Khi ở trạng thái &lt;color=Highlight&gt;Starlume Acceleration&lt;/color&gt;, kích hoạt Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; sẽ phục hồi thêm {3} điểm &lt;color=Highlight&gt;Tần Số Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23482,7 +23482,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Starlume Acceleration&lt;/color&gt;, sử dụng Resonance Liberation &lt;color=Highlight&gt;Heavenfall Edict: Overdrive&lt;/color&gt; sẽ hồi phục thêm &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Gia Tốc Sao Lấp Lánh&lt;/color&gt;, sử dụng Resonance Liberation &lt;color=Highlight&gt;Thiên Lệnh Sụp Đổ: Quá Tải&lt;/color&gt; sẽ hồi phục thêm &lt;color=Highlight&gt;Tần Số Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Includes &lt;color=Highlight&gt;Seraphic Duet: Overture&lt;/color&gt; và &lt;color=Highlight&gt;Seraphic Duet: Encore&lt;/color&gt;.</t>
+          <t>Bao gồm &lt;color=Highlight&gt;Seraphic Duet: Overture&lt;/color&gt; và &lt;color=Highlight&gt;Seraphic Duet: Encore&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23612,7 +23612,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Includes &lt;color=Highlight&gt;Sync Strike: Armament Merge&lt;/color&gt; và &lt;color=Highlight&gt;Sync Strike: Call of Dawn&lt;/color&gt;.</t>
+          <t>Bao gồm &lt;color=Highlight&gt;Sync Strike: Armament Merge&lt;/color&gt; và &lt;color=Highlight&gt;Sync Strike: Call of Dawn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23678,8 +23678,8 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Starflux&lt;/color&gt; bị giới hạn ở mức {0} điểm.
-&lt;color=Highlight&gt;Starflux&lt;/color&gt; sẽ tự phục hồi theo thời gian.</t>
+          <t>&lt;color=Highlight&gt;Dòng Sao&lt;/color&gt; bị giới hạn ở mức {0} điểm.
+&lt;color=Highlight&gt;Dòng Sao&lt;/color&gt; sẽ tự phục hồi theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, kỹ năng Resonance &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; sẽ loại bỏ các lớp &lt;color=Highlight&gt;Rupturous Trail&lt;/color&gt; trên các mục tiêu xung quanh và gây thêm {2} lần &lt;color=Highlight&gt;Tune Rupture DMG&lt;/color&gt;, mỗi lần ngẫu nhiên lên một mục tiêu trong phạm vi. Mỗi lớp &lt;color=Highlight&gt;Rupturous Trail&lt;/color&gt; bị loại bỏ khỏi mục tiêu sẽ tăng Hệ Số Sát Thương của Tune Vỡ do &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; gây ra lên mục tiêu đó thêm {0}. Hiệu ứng này kéo dài trong {1} giây. &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu không ảnh hưởng đến việc kích hoạt các lần Sát Thương Tune Vỡ này.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Điệu Vỡ&lt;/color&gt;, kỹ năng Cộng Hưởng &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt; sẽ loại bỏ các lớp &lt;color=Highlight&gt;Vệt Điệu Vỡ&lt;/color&gt; trên các mục tiêu xung quanh và gây thêm {2} lần &lt;color=Highlight&gt;Sát Thương Điệu Vỡ&lt;/color&gt;, mỗi lần ngẫu nhiên lên một mục tiêu trong phạm vi. Mỗi lớp &lt;color=Highlight&gt;Vệt Điệu Vỡ&lt;/color&gt; bị loại bỏ khỏi mục tiêu sẽ tăng Hệ Số Sát Thương của Điệu Vỡ do &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt; gây ra lên mục tiêu đó thêm {0}. Hiệu ứng này kéo dài trong {1} giây. &lt;color=Highlight&gt;Mức Lệch Điệu&lt;/color&gt; của mục tiêu không ảnh hưởng đến việc kích hoạt các lần Sát Thương Điệu Vỡ này.</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, kỹ năng Resonance &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; sẽ loại bỏ các lớp &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt; trên mục tiêu nếu chúng bị ảnh hưởng bởi &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt;, đồng thời kích hoạt &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt; trên mục tiêu dựa trên giới hạn lớp tối đa mà không loại bỏ các lớp hiện có. Mỗi lớp &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt; bị loại bỏ khỏi mục tiêu sẽ tăng Hệ Số Sát Thương của &lt;color=Highlight&gt;Fusion Trail&lt;/color&gt; lên mục tiêu chính thêm {0}.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Bùng Nổ Dung Hợp&lt;/color&gt;, kỹ năng Cộng Hưởng &lt;color=Highlight&gt;Bản Duet Thiên Thần&lt;/color&gt; sẽ loại bỏ các lớp &lt;color=Highlight&gt;Vệt Dung Hợp&lt;/color&gt; trên mục tiêu nếu chúng bị ảnh hưởng bởi &lt;color=Highlight&gt;Vệt Dung Hợp&lt;/color&gt;, đồng thời kích hoạt &lt;color=Highlight&gt;Vệt Dung Hợp&lt;/color&gt; trên mục tiêu dựa trên giới hạn lớp tối đa mà không loại bỏ các lớp hiện có. Mỗi lớp &lt;color=Highlight&gt;Vệt Dung Hợp&lt;/color&gt; bị loại bỏ khỏi mục tiêu sẽ tăng Hệ Số Sát Thương của &lt;color=Highlight&gt;Vệt Dung Hợp&lt;/color&gt; lên mục tiêu chính thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -23942,7 +23942,7 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>Tối đa {0} điểm.
-Các đòn Normal Attack, Resonance Skill &lt;color=Highlight&gt;Golden Reflux&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Golden Impale&lt;/color&gt; và &lt;color=Highlight&gt;Mid-air Attack - Gavel of Earthshaker&lt;/color&gt; sẽ hồi Ichor Flow khi trúng mục tiêu.
+Các đòn Normal Attack, Resonance Skill &lt;color=Highlight&gt;Golden Reflux&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Golden Impale&lt;/color&gt; và &lt;color=Highlight&gt;Tấn Công Giữa Không - Gavel of Earthshaker&lt;/color&gt; sẽ hồi Ichor Flow khi trúng mục tiêu.
 Sử dụng Kỹ Năng Giới Thiệu &lt;color=Highlight&gt;Before Injection of Dawn&lt;/color&gt; sẽ hồi {1} điểm Ichor Flow.</t>
         </is>
       </c>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tối đa {0} lớp. Khi nhận sát thương từ kẻ địch, tiêu hao &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} để giảm {2} sát thương nhận vào và miễn nhiễm với hiệu ứng gián đoạn trong {3} giây. Hiệu ứng này có thể kích hoạt {4} lần mỗi giây.</t>
+          <t>Tối đa {0} lớp. Khi nhận DMG từ kẻ địch, tiêu hao &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} để giảm {2} DMG nhận vào và miễn nhiễm với hiệu ứng gián đoạn trong {3} giây. Hiệu ứng này có thể kích hoạt {4} lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -24073,7 +24073,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương và {1} Sát Thương từ Basic Attack.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương và {1} Sát Thương từ Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -24139,8 +24139,8 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Resonance Mode - Tune Rupture đang kích hoạt.
-Các Resonators Demo sẽ kế thừa các nút Chuỗi Resonance từ Resonators của ngươi.</t>
+          <t>Chế Độ Cộng Hưởng - Đứt Gãy Giai Điệu đang kích hoạt.
+Các Resonator Demo sẽ kế thừa các nút Resonance Chain từ Resonator của ngươi.</t>
         </is>
       </c>
     </row>
@@ -24208,10 +24208,10 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;, được tính là sát thương Kỹ Năng Basic và không bị ảnh hưởng bởi bất kỳ hiệu ứng Tăng Sát Thương nào.
-Chỉ có thể tồn tại một &lt;color=Highlight&gt;Ichor Blade&lt;/color&gt; tại cùng một thời điểm. Nó không thể kích hoạt &lt;color=Highlight&gt;Counterattack&lt;/color&gt;.
-&lt;color=Highlight&gt;Ichor Blade&lt;/color&gt; không thể phóng ra nếu không có mục tiêu gần đó.
-&lt;color=Highlight&gt;Ichor Blade&lt;/color&gt; sẽ biến mất khi Luuk Herssen sử dụng các kỹ năng khác gây sát thương hoặc rời khỏi chiến trường.</t>
+          <t>Gây &lt;color=Light&gt;DMG Spectro cố định&lt;/color&gt;, được tính là DMG Kỹ Năng Cơ Bản và không bị ảnh hưởng bởi bất kỳ hiệu ứng Tăng Sát Thương nào.
+Chỉ có thể tồn tại một &lt;color=Highlight&gt;Lưỡi Kiếm Ichor&lt;/color&gt; tại cùng một thời điểm. Nó không thể kích hoạt &lt;color=Highlight&gt;Phản Đòn&lt;/color&gt;.
+&lt;color=Highlight&gt;Lưỡi Kiếm Ichor&lt;/color&gt; không thể phóng ra nếu không có mục tiêu gần đó.
+&lt;color=Highlight&gt;Lưỡi Kiếm Ichor&lt;/color&gt; sẽ biến mất khi Luuk Herssen sử dụng các kỹ năng khác gây DMG hoặc rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Ichor Deposit&lt;/color&gt; sẽ tự kích nổ sau {0} giây, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;, được tính là sát thương Basic Attack.</t>
+          <t>&lt;color=Highlight&gt;Mỏ Dưỡng Chất&lt;/color&gt; sẽ tự kích nổ sau {0} giây, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;, được tính là DMG Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Thundering Mephis, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Thundering Mephis, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Nameless Explorer, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Nameless Explorer, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Impermanence Heron, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Impermanence Heron, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -24536,7 +24536,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Sigillum, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Sigillum, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -24603,7 +24603,7 @@
       <c r="M349" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Matrix Mimic&lt;/color&gt;
-Trong 15 giây sau khi đánh bại Matrix Mimic, tất cả Resonators trong đội đều miễn nhiễm với sát thương.</t>
+Trong 15 giây sau khi đánh bại Matrix Mimic, tất cả Resonator trong đội đều miễn nhiễm với sát thương.</t>
         </is>
       </c>
     </row>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Giảm 10% lượng Vibration Strength Reduction mà Thundering Mephis phải chịu. Khi Thundering Mephis bị phản công, nó tích lũy 10% &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; tối đa. Hiệu ứng này có Cooldown chiêu 10 giây. Sau khi Thundering Mephis chịu &lt;color=Highlight&gt;Tune Break DMG&lt;/color&gt;, lượng Vibration Strength Reduction mà nó phải chịu sẽ tăng thêm 30% trong 8 giây.</t>
+          <t>Giảm 10% lượng Giảm Cường Độ Rung Động mà Thundering Mephis phải chịu. Khi Thundering Mephis bị phản công, nó tích lũy 10% &lt;color=Highlight&gt;Mức Lệch Nhịp&lt;/color&gt; tối đa. Hiệu ứng này có thời gian hồi chiêu 10 giây. Sau khi Thundering Mephis chịu &lt;color=Highlight&gt;Sát Thương Vỡ Nhịp&lt;/color&gt;, lượng Giảm Cường Độ Rung Động mà nó phải chịu sẽ tăng thêm 30% trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Sigillum giảm 25% Sát Thương nhận vào. Khi Sigillum chịu &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;, Vibration Strength Động của nó sẽ giảm 3%. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
+          <t>Sigillum giảm 25% Sát Thương nhận vào. Khi Sigillum chịu &lt;color=Highlight&gt;Sát Thương Kỹ Năng Echo&lt;/color&gt;, Độ Mạnh Rung Động của nó sẽ giảm 3%. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24865,7 +24865,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại một Matrix Mimic, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại một Matrix Mimic, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -24930,7 +24930,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tấn Công của Mephis Sấm Sét tăng 3% mỗi 5 giây, tối đa 10 tầng. Choáng nó sẽ xóa toàn bộ tầng cộng dồn và tạm dừng việc cộng dồn.</t>
+          <t>ATK của Mephis Sấm Sét tăng 3% mỗi 5 giây, tối đa 10 tầng. Choáng nó sẽ xóa toàn bộ tầng cộng dồn và tạm dừng việc cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -24995,7 +24995,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Khi Nameless Explorer không chịu ảnh hưởng của &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, Tấn Công của nó tăng 50%. Hiệu ứng này tạm thời vô hiệu trong 12 giây khi Nameless Explorer chịu sát thương Tune Break.</t>
+          <t>Khi Nhà Thám Hiểm Vô Danh không chịu ảnh hưởng của &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, ATK của nó tăng 50%. Hiệu ứng này tạm thời vô hiệu trong 12 giây khi Nhà Thám Hiểm Vô Danh chịu DMG Tune Break.</t>
         </is>
       </c>
     </row>
@@ -25128,8 +25128,8 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại một Matrix Mimic, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với sát thương.
-Echo này có Kháng ngang bằng với mọi loại Sát Thương Thuộc Tính, và điểm nhận được từ nó sẽ được nhân lên &lt;color=Highlight&gt;1.1&lt;/color&gt; lần.</t>
+          <t>Sau khi đánh bại một Matrix Mimic, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với DMG.
+Tổ Tacet này có Kháng ngang bằng với mọi loại Sát Thương Thuộc Tính, và điểm nhận được từ nó sẽ được nhân lên &lt;color=Highlight&gt;1.1&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -25198,11 +25198,11 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Thundering Mephis&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Mephis Sấm Sét, tất cả Resonators trong đội miễn nhiễm sát thương.
-- Tấn Công của Mephis Sấm Sét tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Khi bị Hóa Đá, tất cả cộng dồn sẽ bị xóa và tạm dừng. Khi Mephis Sấm Sét bị phản đòn, nó tích lũy 10% &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; tối đa. Hiệu ứng này có Cooldown 10 giây.
-- Sau khi Mephis Sấm Sét chịu &lt;color=Highlight&gt;Tune Break DMG&lt;/color&gt;, hiệu ứng Giảm Sức Vibration mà nó phải chịu tăng thêm 30% trong 8 giây.
-- Hiệu ứng Giảm Sức Vibration mà Mephis Sấm Sét phải chịu giảm 20%.</t>
+          <t>&lt;color=Highlight&gt;Mephis Sấm Sét&lt;/color&gt;
+- Trong 15 giây sau khi đánh bại Mephis Sấm Sét, tất cả Resonator trong đội miễn nhiễm DMG.
+- ATK của Mephis Sấm Sét tăng 3% mỗi 5 giây, tối đa 10 lần cộng dồn. Khi bị Hóa Đá, tất cả cộng dồn sẽ bị xóa và tạm dừng. Khi Mephis Sấm Sét bị phản đòn, nó tích lũy 10% &lt;color=Highlight&gt;Mức Độ Lệch Nhịp&lt;/color&gt; tối đa. Hiệu ứng này có thời gian hồi 10 giây.
+- Sau khi Mephis Sấm Sét chịu &lt;color=Highlight&gt;Sát Thương Phá Nhịp&lt;/color&gt;, hiệu ứng Giảm Sức Rung động mà nó phải chịu tăng thêm 30% trong 8 giây.
+- Hiệu ứng Giảm Sức Rung động mà Mephis Sấm Sét phải chịu giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -25270,10 +25270,10 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Nameless Explorer&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Nameless Explorer, tất cả Resonators trong đội đều miễn nhiễm với sát thương.
-- Khi Nameless Explorer chịu &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, mức deplete Vibration Strength mà nó nhận được tăng thêm 30%.
-- Khi Nameless Explorer không chịu &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, Tấn Công của nó tăng 50%. Hiệu ứng này tạm thời bị vô hiệu trong 12 giây khi Nameless Explorer chịu Sát Thương Đứt Tần Số.</t>
+          <t>&lt;color=Highlight&gt;Nhà Thám Hiểm Vô Danh&lt;/color&gt;
+- Trong 15 giây sau khi đánh bại Nhà Thám Hiểm Vô Danh, tất cả Resonator trong đội đều miễn nhiễm với DMG.
+- Khi Nhà Thám Hiểm Vô Danh chịu &lt;color=Highlight&gt;Tần Số Quá Tải - Giao Thoa&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tần Số Quá Tải - Biến Đổi&lt;/color&gt;, mức Giảm Sức Rung mà nó nhận được tăng thêm 30%.
+- Khi Nhà Thám Hiểm Vô Danh không chịu &lt;color=Highlight&gt;Tần Số Quá Tải - Giao Thoa&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tần Số Quá Tải - Biến Đổi&lt;/color&gt;, ATK của nó tăng 50%. Hiệu ứng này tạm thời bị vô hiệu trong 12 giây khi Nhà Thám Hiểm Vô Danh chịu Sát Thương Đứt Tần Số.</t>
         </is>
       </c>
     </row>
@@ -25341,10 +25341,10 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Impermanence Heron&lt;/color&gt;
-- Trong 15 giây sau khi đánh bại Impermanence Heron, tất cả Resonators trong đội đều miễn nhiễm sát thương.
-- Khi Impermanence Heron tấn công Resonators, mục tiêu sẽ mất 4% HP tối đa mỗi giây trong 6 giây khi đang ở trên chiến trường, và 2% HP tối đa mỗi giây trong 6 giây khi rời khỏi chiến trường. Hiệu ứng này không thể hạ HP xuống 0.
-- Khi HP của Resonators trên 50%, Impermanence Heron chịu thêm 10% tổng sát thương.</t>
+          <t>&lt;color=Highlight&gt;Diệc Vô Thường&lt;/color&gt;
+- Trong 15 giây sau khi đánh bại Diệc Vô Thường, tất cả Resonator trong đội đều miễn nhiễm DMG.
+- Khi Diệc Vô Thường tấn công Resonator, mục tiêu sẽ mất 4% HP tối đa mỗi giây trong 6 giây khi đang ở trên chiến trường, và 2% HP tối đa mỗi giây trong 6 giây khi rời khỏi chiến trường. Hiệu ứng này không thể hạ HP xuống 0.
+- Khi HP của Resonator trên 50%, Diệc Vô Thường chịu thêm 10% tổng DMG.</t>
         </is>
       </c>
     </row>
@@ -25413,9 +25413,9 @@
       <c r="M361" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Sigillum&lt;/color&gt;
-- Sau khi đánh bại Sigillum, tất cả Resonators trong đội sẽ miễn nhiễm sát thương trong 15 giây.
-- Khi Sigillum chịu &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;, Concerto Vibrancy của nó giảm 3%. Hiệu ứng này có Cooldown 2 giây.
-- Mức giảm Concerto Vibrancy mà Sigillum phải chịu giảm 20%.</t>
+- Sau khi đánh bại Sigillum, tất cả Resonator trong đội sẽ miễn nhiễm DMG trong 15 giây.
+- Khi Sigillum chịu &lt;color=Highlight&gt;Sát Thương Kỹ Năng Echo&lt;/color&gt;, Sức Mạnh Rung Động của nó giảm 3%. Hiệu ứng này có thời gian hồi 2 giây.
+- Mức giảm Sức Mạnh Rung Động mà Sigillum phải chịu giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -25483,8 +25483,8 @@
       <c r="M362" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Matrix Mimic&lt;/color&gt;
-- Echo này có Kháng như nhau với mọi loại Sát Thương Thuộc Tính, và điểm nhận được từ nó sẽ nhân lên &lt;color=Highlight&gt;1,1&lt;/color&gt; lần.
-- Trong 15 giây sau khi đánh bại Matrix Mimic, tất cả Resonators trong đội đều miễn nhiễm với sát thương.</t>
+- Tổ Tacet này có Kháng như nhau với mọi loại Sát Thương Thuộc Tính, và điểm nhận được từ nó sẽ nhân lên &lt;color=Highlight&gt;1,1&lt;/color&gt; lần.
+- Trong 15 giây sau khi đánh bại Matrix Mimic, tất cả Resonator trong đội đều miễn nhiễm với DMG.</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng sát thương nhận vào tăng thêm {0} trong {1} giây. Khi bị Spectro Frazzle, Spectro DMG Frazzle nhận vào tăng thêm {2}.</t>
+          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng DMG nhận vào tăng thêm {0} trong {1} giây. Khi bị Spectro Frazzle, DMG Spectro Frazzle nhận vào tăng thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Kỹ Năng Echo. Tăng {1} Aero DMG Total.</t>
+          <t>Tăng {0} Sát Thương Kỹ Năng Echo. Tăng {1} Sát Thương Aero Tổng.</t>
         </is>
       </c>
     </row>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương và {1} Sát Thương từ Heavy Attack.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương và {1} Sát Thương từ Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Status Tiêu cực</t>
+          <t>Negative Status</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Đánh bại 8 kẻ địch trong Singularity Expansion (Đặt lại mỗi giai đoạn)</t>
+          <t>Hạ gục 8 kẻ địch trong Khu Vực Kỳ Dị (Đặt lại mỗi giai đoạn)</t>
         </is>
       </c>
     </row>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Dùng 2 đội đánh bại 2 kẻ địch sau Round 2 trong Singularity Expansion (Đặt lại mỗi giai đoạn)</t>
+          <t>Dùng 2 đội đánh bại 2 kẻ địch sau Vòng 2 trong Singularity Expansion (Đặt lại mỗi giai đoạn)</t>
         </is>
       </c>
     </row>
@@ -26136,7 +26136,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Thu thập 5.000 Points Singularity Expansion trong một trận đấu mà không bị sát thương</t>
+          <t>Thu thập 5.000 Điểm Mở Rộng Điểm Kỳ Dị trong một trận đấu mà không bị sát thương</t>
         </is>
       </c>
     </row>
@@ -26203,9 +26203,9 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Sigrika có thể giữ tối đa &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=0}&lt;/color&gt;. Nếu không có &lt;color=Highlight&gt;Full Stop&lt;/color&gt;, Sigrika chỉ có thể giữ tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=1}&lt;/color&gt;. Khi Sigrika nhận thêm &lt;color=Highlight&gt;Rune&lt;/color&gt; mới ở mức tối đa, các &lt;color=Highlight&gt;Runes&lt;/color&gt; hiện có sẽ dịch chuyển một ô sang trái, và &lt;color=Highlight&gt;Rune&lt;/color&gt; ngoài cùng bên trái sẽ bị loại bỏ. Với ít nhất &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} &lt;color=Highlight&gt;Full Stop&lt;/color&gt;, Sigrika có thể giữ thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=3}.
-Đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Basic Attack - Elucidated&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Decipher&lt;/color&gt; trong thời gian thi triển sẽ nhận được một &lt;color=Highlight&gt;Rune: Trust&lt;/color&gt;.
-Đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Resonance Skill - BIG BOOMY BOOM!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin to the Aid&lt;/color&gt; trong thời gian thi triển sẽ nhận được một &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
+          <t>Sigrika có thể giữ tối đa &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=0}&lt;/color&gt;. Nếu không có &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, Sigrika chỉ có thể giữ tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=1}&lt;/color&gt;. Khi Sigrika nhận thêm &lt;color=Highlight&gt;Rune&lt;/color&gt; mới ở mức tối đa, các &lt;color=Highlight&gt;Rune&lt;/color&gt; hiện có sẽ dịch chuyển một ô sang trái, và &lt;color=Highlight&gt;Rune&lt;/color&gt; ngoài cùng bên trái sẽ bị loại bỏ. Với ít nhất &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, Sigrika có thể giữ thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=Rune P=Rune SapTag=3}.
+Đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Đòn Cơ Bản - Giải Thích&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter Tránh - Giải Mã&lt;/color&gt; trong thời gian thi triển sẽ nhận được một &lt;color=Highlight&gt;Rune: Niềm Tin&lt;/color&gt;.
+Đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Resonance Skill - NỔ TOANG ĐÂY!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin Giúp Sức&lt;/color&gt; trong thời gian thi triển sẽ nhận được một &lt;color=Highlight&gt;Rune: Lời Đáp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Schemata of Runes&lt;/color&gt;, nhận được {0} điểm &lt;color=Highlight&gt;Full Stop&lt;/color&gt;, tối đa 100 điểm.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Sơ Đồ Rune&lt;/color&gt;, nhận được {0} điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, tối đa 100 điểm.</t>
         </is>
       </c>
     </row>
@@ -26336,7 +26336,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Sigrika có thể tích lũy tối đa &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} &lt;color=Highlight&gt;Innate Gift?&lt;/color&gt;. Mỗi lớp tăng cường {1} Sát Thương cho &lt;color=Highlight&gt;Runic Outburst&lt;/color&gt;, &lt;color=Highlight&gt;Runic Chain Whip&lt;/color&gt;, &lt;color=Highlight&gt;Runic Soliskin&lt;/color&gt; và &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.
+          <t>Sigrika có thể tích lũy tối đa &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} &lt;color=Highlight&gt;Tài Năng Bẩm Sinh?&lt;/color&gt;. Mỗi lớp tăng cường {1} Sát Thương cho &lt;color=Highlight&gt;Runic Outburst&lt;/color&gt;, &lt;color=Highlight&gt;Runic Chain Whip&lt;/color&gt;, &lt;color=Highlight&gt;Runic Soliskin&lt;/color&gt; và &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.
 Hiệu ứng này sẽ kết thúc sau khi Sigrika sử dụng &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt; hoặc bị thay ra khỏi trận đấu.</t>
         </is>
       </c>
@@ -26540,7 +26540,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonators gần đó trong đội sử dụng Kỹ Năng Echoes, Sigrika nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} &lt;color=Highlight&gt;Soliskin Vitality&lt;/color&gt;, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1}. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Sử dụng &lt;color=Highlight&gt;Outro Skill - In This Very Moment&lt;/color&gt; sẽ reset bản ghi kích hoạt hiệu ứng của Echoes.</t>
+          <t>Khi bất kỳ Resonator gần đó trong đội sử dụng Kỹ Năng Echo, Sigrika nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} &lt;color=Highlight&gt;Sinh Khí Soliskin&lt;/color&gt;, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1}. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Sử dụng &lt;color=Highlight&gt;Kỹ Năng Outro - Trong Chính Khoảnh Khắc Này&lt;/color&gt; sẽ reset bản ghi kích hoạt hiệu ứng của Echo.</t>
         </is>
       </c>
     </row>
@@ -26605,7 +26605,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Matrix Mimic có khả năng kháng tất cả thuộc tính sát thương như nhau. Gây sát thương lên nó sẽ nhận được &lt;color=Highlight&gt;1.1x&lt;/color&gt; điểm.</t>
+          <t>Bắt Chước Ma Trận có khả năng kháng tất cả thuộc tính DMG như nhau. Gây DMG lên nó sẽ nhận được &lt;color=Highlight&gt;1.1x&lt;/color&gt; điểm.</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; trong {0} giây. Hiệu ứng kết thúc sớm nếu Sigrika rời khỏi chiến trường.</t>
+          <t>Vào trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt; trong {0} giây. Hiệu ứng kết thúc sớm nếu Sigrika rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -26736,8 +26736,8 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonators gần đó trong đội sử dụng Skills Echo, mục tiêu sẽ bị Trì Hoãn và tiêu hao &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} &lt;color=Highlight&gt;Encapsulated&lt;/color&gt;. &lt;color=Highlight&gt;Encapsulated&lt;/color&gt; có thể tích lũy tối đa {1} lần.
-Tất cả lớp &lt;color=Highlight&gt;Encapsulated&lt;/color&gt; sẽ bị xóa khi Sigrika rời đội hình.</t>
+          <t>Khi bất kỳ Resonator gần đó trong đội sử dụng Kỹ Năng Echo, mục tiêu sẽ bị Trì Hoãn và tiêu hao &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} &lt;color=Highlight&gt;Bọc Tĩnh&lt;/color&gt;. &lt;color=Highlight&gt;Bọc Tĩnh&lt;/color&gt; có thể tích lũy tối đa {1} lần.
+Tất cả lớp &lt;color=Highlight&gt;Bọc Tĩnh&lt;/color&gt; sẽ bị xóa khi Sigrika rời đội hình.</t>
         </is>
       </c>
     </row>
@@ -26803,8 +26803,8 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng sát thương nhận vào tăng thêm {0}, và Glacio DMG nhận vào tăng thêm {1} trong {2} giây.
-Kẻ địch chịu thêm {3} sát thương từ Glacio Chafe và Fusion Burst.</t>
+          <t>Khi kẻ địch bị dính trạng thái tiêu cực, tổng DMG nhận vào tăng thêm {0}, và DMG Glacio nhận vào tăng thêm {1} trong {2} giây.
+Kẻ địch chịu thêm {3} DMG từ Glacio Chafe và Fusion Burst.</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Kỹ Năng Echo. Tăng {1} Havoc DMG Total. Tăng {2} Sát Thương Resonance Skill.</t>
+          <t>Tăng {0} Sát Thương Kỹ Năng Echo. Tăng {1} Sát Thương Havoc Tổng. Tăng {2} Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -26935,8 +26935,8 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Khi Resonators gây hiệu ứng Điều Tiết - Dịch Chuyển, tổng sát thương của Resonators trong đội sẽ tăng thêm {0} trong 30 giây.
-Khi Resonators gây hiệu ứng Căng Âm - Dịch Chuyển, tổng sát thương của họ sẽ tăng thêm {1} trong 15 giây.</t>
+          <t>Khi Resonator gây hiệu ứng Điều Tiết - Dịch Chuyển, tổng DMG của các Resonator trong đội sẽ tăng thêm {0} trong 30 giây.
+Khi Resonator gây hiệu ứng Căng Âm - Dịch Chuyển, tổng DMG của họ sẽ tăng thêm {1} trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -27001,7 +27001,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mục tiêu chịu thêm {0} Total Sát Thương và {1} Sát Thương Resonance Liberation.</t>
+          <t>Mục tiêu chịu thêm {0} Tổng Sát Thương và {1} Sát Thương Giải Cứu Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Reactor Husk, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Reactor Husk, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại Scar, trong 15 giây, tất cả Resonators trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
+          <t>Sau khi đánh bại Scar, trong 15 giây, tất cả Resonator trong đội miễn nhiễm với mọi loại sát thương và gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -27196,7 +27196,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tấn Công của Reactor Husk tăng 20%. Sau khi chịu Sát Thương Status Tiêu Cực, thay vào đó, Tấn Công của Reactor Husk sẽ giảm 20%.</t>
+          <t>ATK của Vỏ Lò Phản Ứng tăng 20%. Sau khi chịu Sát Thương Trạng Thái Tiêu Cực, thay vào đó, ATK của Vỏ Lò Phản Ứng sẽ giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -27264,8 +27264,8 @@
       <c r="M389" t="inlineStr">
         <is>
           <t>Khi Scar tấn công Resonator, mục tiêu sẽ mất 3% HP tối đa mỗi giây trong 6 giây khi ở trên chiến trường. Hiệu ứng này không thể hạ HP xuống 0.
-Khi HP của Resonator ở mức đầy, Tỷ Lệ deplete Vibration Strength của họ tăng 40%.
-Scar chịu thêm 100% Fusion DMG Burst. Sau khi nhận Sát Thương Status Tiêu Cực, các đòn tấn công của Scar sẽ không còn gây hiệu ứng giảm HP.</t>
+Khi HP của Resonator ở mức đầy, Tỷ Lệ Giảm Sức Rung của họ tăng 40%.
+Scar chịu thêm 100% Sát Thương Fusion Burst. Sau khi nhận Sát Thương Trạng Thái Tiêu Cực, các đòn tấn công của Scar sẽ không còn gây hiệu ứng giảm HP.</t>
         </is>
       </c>
     </row>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tấn Công của Reactor Husk tăng vĩnh viễn 25%.</t>
+          <t>ATK của Reactor Husk tăng vĩnh viễn 25%.</t>
         </is>
       </c>
     </row>
@@ -27463,10 +27463,10 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Khi cầm &lt;color=Highlight&gt;Dark Core&lt;/color&gt;, kỹ năng Resonance &lt;color=Highlight&gt;Beckon - Breakdown Form&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Banish - Breakdown Form&lt;/color&gt;.
-- Denia có thể giữ tối đa {0} &lt;color=Highlight&gt;Dark Cores&lt;/color&gt;.
-- Khi ở trạng thái &lt;color=Highlight&gt;Entropy Shift&lt;/color&gt;, Denia nhận được {2} &lt;color=Highlight&gt;Dark Core&lt;/color&gt; sau mỗi {1} giây.
-- Sử dụng Intro Skill &lt;color=Highlight&gt;It's Been A While!&lt;/color&gt; và Intro Skill &lt;color=Highlight&gt;Knock Knock&lt;/color&gt; sẽ nhận được &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Dark Core P=Dark Cores SapTag=3}&lt;/color&gt;.</t>
+          <t>Khi cầm &lt;color=Highlight&gt;Hạt Tối&lt;/color&gt;, kỹ năng Cộng Hưởng &lt;color=Highlight&gt;Triệu Hoán - Hình Thức Phân Rã&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Trục Xuất - Hình Thức Phân Rã&lt;/color&gt;.
+- Denia có thể giữ tối đa {0} &lt;color=Highlight&gt;Hạt Tối&lt;/color&gt;.
+- Khi ở trạng thái &lt;color=Highlight&gt;Dịch Chuyển Entropy&lt;/color&gt;, Denia nhận được {2} &lt;color=Highlight&gt;Hạt Tối&lt;/color&gt; sau mỗi {1} giây.
+- Sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Lâu Lắm Không Gặp!&lt;/color&gt; và Kỹ Năng Khởi Động &lt;color=Highlight&gt;Cốc Cốc!&lt;/color&gt; sẽ nhận được &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Hạt Tối P=Hạt Tối SapTag=3}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27536,12 +27536,12 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt; và đang giữ &lt;color=Highlight&gt;Void Particle&lt;/color&gt;, &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Void Particle&lt;/color&gt; khi trúng mục tiêu và mang lại các hiệu ứng sau:
-- Sát thương kỹ năng được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt; và Hệ Số Sát Thương tăng thêm {0}.
-- &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; hồi phục nhanh hơn {1}.
-Denia có thể giữ tối đa {2} điểm &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.
-- Khi ở &lt;color=Highlight&gt;Stagecraft Form&lt;/color&gt;, gây sát thương bằng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.
-- Sử dụng Intro Skill &lt;color=Highlight&gt;It's Been A While!&lt;/color&gt;, Intro Skill &lt;color=Highlight&gt;Knock Knock&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Phantom Bubble - Stagecraft Form&lt;/color&gt; sẽ nhận được &lt;SapTag=D&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=D} &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Hình Thái Phân Rã&lt;/color&gt; và đang giữ &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; sẽ tiêu hao &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt; khi trúng mục tiêu và mang lại các hiệu ứng sau:
+- DMG kỹ năng được tính là &lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; và Hệ Số Sát Thương tăng thêm {0}.
+- &lt;color=Highlight&gt;Điện Tích Đồng Dạng&lt;/color&gt; hồi phục nhanh hơn {1}.
+Denia có thể giữ tối đa {2} điểm &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt;.
+- Khi ở &lt;color=Highlight&gt;Hình Thái Diễn Xuất&lt;/color&gt;, gây DMG bằng &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt;.
+- Sử dụng Kỹ Năng Khởi Động &lt;color=Highlight&gt;Lâu Lắm Không Gặp!&lt;/color&gt;, Kỹ Năng Khởi Động &lt;color=Highlight&gt;Cốc Cốc!&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Bong Bóng Ảo - Hình Thái Diễn Xuất&lt;/color&gt; sẽ nhận được &lt;SapTag=D&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=D} &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27607,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Increases ATK by {0}.
+          <t>Tăng ATK {0}.
 Kích hoạt hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Entropy Shift: Stagecraft Form&lt;/color&gt;.</t>
         </is>
       </c>
@@ -27674,8 +27674,8 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Mỗi giây nhận được {0} &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.
-Kích hoạt hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Entropy Shift: Breakdown Form&lt;/color&gt;.</t>
+          <t>Mỗi giây nhận được {0} &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.
+Kích hoạt hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Dịch Chuyển Entropy: Hình Thái Phân Rã&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27743,10 +27743,10 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; đầy, tiêu hao toàn bộ &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; và &lt;color=Highlight&gt;Void Particle&lt;/color&gt; để thực hiện Resonance Liberation &lt;color=Highlight&gt;Final Act - Breakdown Form&lt;/color&gt;.
-- Denia có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt;.
-- Trong &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;, gây sát thương bằng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Beckon - Breakdown Form&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt;.
-- Sử dụng Resonance Skill &lt;color=Highlight&gt;Banish - Breakdown Form Stage 2&lt;/color&gt; sẽ nhận được &lt;SapTag=F&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Nạp Thuận Hóa&lt;/color&gt; đầy, tiêu hao toàn bộ &lt;color=Highlight&gt;Nạp Thuận Hóa&lt;/color&gt; và &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt; để thực hiện Resonance Liberation &lt;color=Highlight&gt;Hồi Kết - Dạng Phân Rã&lt;/color&gt;.
+- Denia có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Nạp Thuận Hóa&lt;/color&gt;.
+- Trong &lt;color=Highlight&gt;Dạng Phân Rã&lt;/color&gt;, gây sát thương bằng &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Triệu Hoán - Dạng Phân Rã&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Nạp Thuận Hóa&lt;/color&gt;.
+- Sử dụng Resonance Skill &lt;color=Highlight&gt;Trục Xuất - Giai Đoạn 2 Dạng Phân Rã&lt;/color&gt; sẽ nhận được &lt;SapTag=F&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} &lt;color=Highlight&gt;Nạp Thuận Hóa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Đánh bại 5 kẻ địch bằng một đội duy nhất trong Singularity Expansion</t>
+          <t>Tiêu diệt 5 kẻ địch trong một đội tại Mở Rộng Đơn Tính</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Gây 7.000.000 Fusion DMG Burst hoặc Glacio Chafe lên kẻ địch trong một trận đấu.</t>
+          <t>Gây 7.000.000 DMG Fusion Burst hoặc Glacio Chafe lên kẻ địch trong một trận đấu.</t>
         </is>
       </c>
     </row>
@@ -27946,12 +27946,12 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Hiyuki có thể tích lũy tối đa 300 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, &lt;color=Highlight&gt;Dedication&lt;/color&gt; có thể được hồi phục bằng các cách sau:
-- Sử dụng &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; sẽ hồi phục 100 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;.
-- Sử dụng &lt;color=Highlight&gt;Intro Skill - Frostedge&lt;/color&gt; sẽ hồi phục 200 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;.
-Sử dụng &lt;color=Highlight&gt;Resonance Skill - Present Self&lt;/color&gt; sẽ tăng cường &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; tiếp theo, đồng thời hồi phục thêm 100 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dedication&lt;/te&gt;&lt;/color&gt;. Hiệu ứng này sẽ mất khi Hiyuki rời trận.
-Khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt; sẽ được kích hoạt.</t>
+          <t>Hiyuki có thể tích lũy tối đa 300 điểm &lt;color=Highlight&gt;Dốc Lòng&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;, &lt;color=Highlight&gt;Dốc Lòng&lt;/color&gt; có thể được hồi phục bằng các cách sau:
+- Sử dụng &lt;color=Highlight&gt;Đòn Cơ Bản - Bản Ngã Hiện Tại Cấp 3&lt;/color&gt; sẽ hồi phục 100 điểm &lt;color=Highlight&gt;Dốc Lòng&lt;/color&gt;.
+- Sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động - Frostedge&lt;/color&gt; sẽ hồi phục 200 điểm &lt;color=Highlight&gt;Dốc Lòng&lt;/color&gt;.
+Sử dụng &lt;color=Highlight&gt;Resonance Skill - Bản Ngã Hiện Tại&lt;/color&gt; sẽ tăng cường &lt;color=Highlight&gt;Đòn Cơ Bản - Bản Ngã Hiện Tại Cấp 3&lt;/color&gt; tiếp theo, đồng thời hồi phục thêm 100 điểm &lt;color=Highlight&gt;&lt;te href=110801&gt;Dốc Lòng&lt;/te&gt;&lt;/color&gt;. Hiệu ứng này sẽ mất khi Hiyuki rời trận.
+Khi &lt;color=Highlight&gt;Dốc Lòng&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Đòn Nặng - Frost Splinter: Bản Ngã Hiện Tại&lt;/color&gt; sẽ được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -28018,9 +28018,9 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Hiyuki có thể tích lũy tối đa 300 điểm &lt;color=Highlight&gt;Frostheart&lt;/color&gt;.
-&lt;color=Highlight&gt;Frostheart&lt;/color&gt; được hồi phục khi sử dụng &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt; và &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;, hoặc khi &lt;color=Highlight&gt;Normal Attacks - Foreclaimed Self&lt;/color&gt; (ngoại trừ &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;) trúng mục tiêu.
-Nếu Hiyuki có ít nhất 100 điểm &lt;color=Highlight&gt;Frostheart&lt;/color&gt;, cô có thể bước vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;. Khi ở &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; và tiêu hao 100 điểm &lt;color=Highlight&gt;Frostheart&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;.</t>
+          <t>Hiyuki có thể tích lũy tối đa 300 điểm &lt;color=Highlight&gt;Linh Khí Băng&lt;/color&gt;.
+&lt;color=Highlight&gt;Linh Khí Băng&lt;/color&gt; được hồi phục khi sử dụng &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt; và &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;, hoặc khi &lt;color=Highlight&gt;Đòn Thường - Bản Ngã Đã Định&lt;/color&gt; (ngoại trừ &lt;color=Highlight&gt;Đòn Nặng - Bitterfrost: Bản Ngã Đã Định&lt;/color&gt;) trúng mục tiêu.
+Nếu Hiyuki có ít nhất 100 điểm &lt;color=Highlight&gt;Linh Khí Băng&lt;/color&gt;, cô có thể bước vào &lt;color=Highlight&gt;Tư Thế Iai&lt;/color&gt;. Khi ở &lt;color=Highlight&gt;Tư Thế Iai&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Đòn Thường&lt;/color&gt; và tiêu hao 100 điểm &lt;color=Highlight&gt;Linh Khí Băng&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Đòn Cơ Bản - Iai&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28089,7 +28089,7 @@
         <is>
           <t>&lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt; có tối đa 3 điểm.
 Khi sử dụng &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt;, Hiyuki nhận được 3 điểm &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;.
-Mỗi khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Basic - Iai&lt;/color&gt;, nếu Hiyuki đang có &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;, sẽ tiêu hao 1 điểm để gây 3 lớp &lt;color=Highlight&gt;Glacio Chafe&lt;/color&gt; khi trúng mục tiêu, đồng thời nhận 1 lớp &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.</t>
+Mỗi khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Cơ Bản - Iai&lt;/color&gt;, nếu Hiyuki đang có &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;, sẽ tiêu hao 1 điểm để gây 3 lớp &lt;color=Highlight&gt;Glacio Chafe&lt;/color&gt; khi trúng mục tiêu, đồng thời nhận 1 lớp &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28158,9 +28158,9 @@
       <c r="M402" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; có thể tích lũy tối đa 3 tầng.
-Mỗi lần tiêu hao &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt; thông qua &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, nhận 1 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.
-Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;.
-Sử dụng &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt; sẽ tiêu hao 3 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.</t>
+Mỗi lần tiêu hao &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt; thông qua &lt;color=Highlight&gt;Đòn Cơ Bản - Iai&lt;/color&gt;, nhận 1 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.
+Khi &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; đạt tối đa, &lt;color=Highlight&gt;Đòn Nặng - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Nặng - Bitterfrost: Foreclaimed Self&lt;/color&gt;.
+Sử dụng &lt;color=Highlight&gt;Đòn Nặng - Bitterfrost: Foreclaimed Self&lt;/color&gt; sẽ tiêu hao 3 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28228,8 +28228,8 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; có thể cộng dồn tối đa 3 lần.
-Mỗi lần sử dụng &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;, nhận 1 điểm cộng dồn &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, giữ &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để bước vào trạng thái nạp năng lượng, liên tục tiêu hao &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;. Thả &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Hệ số sát thương của đòn tấn công tăng theo mỗi điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; đã tiêu hao khi nạp năng lượng.</t>
+Mỗi lần sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;, nhận 1 điểm cộng dồn &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, giữ &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để bước vào trạng thái nạp năng lượng, liên tục tiêu hao &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;. Thả &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Hệ số DMG của đòn tấn công tăng theo mỗi điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; đã tiêu hao khi nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Hiyuki khởi đầu ở &lt;color=Highlight&gt;Present Self&lt;/color&gt;. Khi ở trong trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; sẽ khôi phục 100 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Resonance Skill - Present Self&lt;/color&gt; sẽ tăng cường &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; tiếp theo, giúp khôi phục thêm 100 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;. Hiệu ứng này sẽ kết thúc khi chuyển sang Resonator khác.</t>
+          <t>Hiyuki khởi đầu ở &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;. Khi ở trong trạng thái &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Đòn Basic Attack - Giai Đoạn 3 Bản Ngã Hiện Tại&lt;/color&gt; sẽ khôi phục 100 điểm &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Resonance Skill - Bản Ngã Hiện Tại&lt;/color&gt; sẽ tăng cường &lt;color=Highlight&gt;Đòn Basic Attack - Giai Đoạn 3 Bản Ngã Hiện Tại&lt;/color&gt; tiếp theo, giúp khôi phục thêm 100 điểm &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt;. Hiệu ứng này sẽ kết thúc khi chuyển sang Resonator khác.</t>
         </is>
       </c>
     </row>
@@ -28359,7 +28359,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt;, Hiyuki sẽ bước vào trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, Hiyuki mở khóa các động tác mới và phục hồi &lt;color=Highlight&gt;Frostheart&lt;/color&gt; thông qua một số đòn tấn công nhất định.</t>
+          <t>Khi kích hoạt &lt;color=Highlight&gt;Tuyên Ngôn: Nội Quan&lt;/color&gt;, Hiyuki sẽ bước vào trạng thái &lt;color=Highlight&gt;Tuyên Ngôn Bản Ngã&lt;/color&gt;. Trong trạng thái này, Hiyuki mở khóa các động tác mới và hồi phục &lt;color=Highlight&gt;Linh Hồn Băng Giá&lt;/color&gt; thông qua một số đòn tấn công.</t>
         </is>
       </c>
     </row>
@@ -28495,13 +28495,13 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Entropy Shift: Stagecraft Form&lt;/color&gt;&lt;/size&gt;
-Mỗi giây nhận được {0} điểm &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.
-Hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Entropy Shift: Breakdown Form&lt;/color&gt;.
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Dịch Chuyển Entropy: Hình Thái Diễn Xuất&lt;/color&gt;&lt;/size&gt;
+Mỗi giây nhận được {0} điểm &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.
+Hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Dịch Chuyển Entropy: Hình Thái Phân Rã&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Entropy Shift: Breakdown Form&lt;/color&gt;&lt;/size&gt;
-Tăng Tấn Công thêm {1}.
-Hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Entropy Shift: Stagecraft Form&lt;/color&gt;.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Dịch Chuyển Entropy: Hình Thái Phân Rã&lt;/color&gt;&lt;/size&gt;
+Tăng ATK thêm {1}.
+Hiệu ứng này sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;Dịch Chuyển Entropy: Hình Thái Diễn Xuất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28567,8 +28567,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Resonance Mode - Tune Rupture đang kích hoạt.
-Các Resonators Demo sẽ kế thừa các nút Chuỗi Resonance từ Resonators của ngươi.</t>
+          <t>Chế Độ Cộng Hưởng - Đứt Gãy Giai Điệu đang kích hoạt.
+Các Resonator Demo sẽ kế thừa các nút Resonance Chain từ Resonator của ngươi.</t>
         </is>
       </c>
     </row>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, Aemeath có thể gây &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt; lên mục tiêu, và &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; có thể gây thêm &lt;color=Highlight&gt;Tune Rupture DMG&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Giai Điệu Vỡ&lt;/color&gt;, Aemeath có thể gây &lt;color=Highlight&gt;Giai Điệu Vỡ - Dịch Chuyển&lt;/color&gt; lên mục tiêu, và &lt;color=Highlight&gt;Bản Duet Thần Thánh&lt;/color&gt; có thể gây thêm &lt;color=Highlight&gt;Sát Thương Giai Điệu Vỡ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28698,7 +28698,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Giai điệu Vỡ</t>
+          <t>Chế Độ Cộng Hưởng - Đứt Gãy Giai Điệu</t>
         </is>
       </c>
     </row>
@@ -28763,7 +28763,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, số lượng tầng cần thiết để kích hoạt &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; giảm đi. Aemeath có thể gây &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; lên mục tiêu, và &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt; có thể kích hoạt &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; dựa trên giới hạn tầng tối đa mà không làm mất tầng.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Cơn Bùng Nổ Dung Nham&lt;/color&gt;, số lượng tầng cần thiết để kích hoạt &lt;color=Highlight&gt;Cơn Bùng Nổ Dung Nham&lt;/color&gt; giảm đi. Aemeath có thể gây &lt;color=Highlight&gt;Cơn Bùng Nổ Dung Nham&lt;/color&gt; lên mục tiêu, và &lt;color=Highlight&gt;Bản Duet Thần Thánh&lt;/color&gt; có thể kích hoạt &lt;color=Highlight&gt;Cơn Bùng Nổ Dung Nham&lt;/color&gt; dựa trên giới hạn tầng tối đa mà không làm mất tầng.</t>
         </is>
       </c>
     </row>
@@ -28828,7 +28828,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Fusion Burst</t>
+          <t>Chế Độ Cộng Hưởng - Bùng Nổ Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -28893,7 +28893,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Fusion Burst</t>
+          <t>Chế Độ Cộng Hưởng - Bùng Nổ Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -28958,7 +28958,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, Resonator này gây &lt;color=Highlight&gt;Fusion Burst Effect&lt;/color&gt; và tăng sát thương của đội hình Effect Cơn Bùng Nổ Dung Nham.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Cơn Bùng Nổ Dung Nham&lt;/color&gt;, Resonator này gây &lt;color=Highlight&gt;Hiệu Ứng Cơn Bùng Nổ Dung Nham&lt;/color&gt; và tăng sát thương của đội hình Hiệu Ứng Cơn Bùng Nổ Dung Nham.</t>
         </is>
       </c>
     </row>
@@ -29023,7 +29023,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Tune Strain&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, đặt lại thời gian &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt;, tăng nhanh &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu và tổng thể tăng sát thương gây ra bởi đội hình Phản Ứng Giai Tune Méo Mó.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Giai Điệu Méo Mó&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Giai Điệu Méo Mó - Dịch Chuyển&lt;/color&gt;, đặt lại thời gian &lt;color=Highlight&gt;Giai Điệu Méo Mó - Giao Thoa&lt;/color&gt;, tăng nhanh &lt;color=Highlight&gt;Mức Độ Lệch Giai Điệu&lt;/color&gt; của mục tiêu và tổng thể tăng sát thương gây ra bởi đội hình Phản Ứng Giai Điệu Méo Mó.</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Chế độ Cộng hưởng - Giai điệu Căng</t>
+          <t>Chế Độ Cộng Hưởng - Căng Thẳng Giai Điệu</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Summon "Kẻ Trêu Giỡn" gây {0} Fusion DMG lên kẻ địch. Trong vòng {1} giây tiếp theo, sử dụng Outro Skill sẽ ban cho Resonator kế tiếp {2} Fusion DMG Bonus trong {3} giây.
+          <t>Triệu hồi "Kẻ Trêu Giỡn" gây {0} Sát Thương Fusion lên kẻ địch. Trong vòng {1} giây tiếp theo, sử dụng Kỹ Năng Outro sẽ ban cho Resonator kế tiếp {2} Tăng Sát Thương Fusion trong {3} giây.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Summon Sáng Tạo Aleph-1 để gây {0} Sát Thương Băng 5 lần và {1} Sát Thương Băng 1 lần lên kẻ địch.
+          <t>Triệu hồi Sáng Tạo Aleph-1 để gây {0} Sát Thương Băng 5 lần và {1} Sát Thương Băng 1 lần lên kẻ địch.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Băng và {3} Tăng Sát Thương Resonance Liberation.
 Hồi chiêu: {4} giây</t>
         </is>
@@ -29290,7 +29290,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Summon Sáng Tạo Aleph-1 để gây Sát Thương Băng.
+          <t>Triệu hồi Sáng Tạo Aleph-1 để gây Sát Thương Băng.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Tăng Sát Thương Băng và Tăng Sát Thương Resonance Liberation.</t>
         </is>
       </c>
@@ -29356,7 +29356,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Summon "Kẻ Trêu Giỡn" gây Fusion DMG lên kẻ địch và tăng Fusion DMG của Resonator kế tiếp sử dụng Intro Skill.</t>
+          <t>Triệu hồi "Kẻ Trêu Giỡn" gây Sát Thương Fusion lên kẻ địch và tăng Sát Thương Fusion của Resonator kế tiếp sử dụng Kỹ Năng Intro.</t>
         </is>
       </c>
     </row>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Jinzhou-Event Nghỉ ngơi-Yangyang Gối Đầu-Phục hồi Cuộn Film</t>
+          <t>Jinzhou-Sự kiện Nghỉ ngơi-Yangyang Gối Đầu-Phục hồi Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -29488,9 +29488,9 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A humanoid Tacet Discord with a body assembled from shattered stained glass. Glittering lights beam from its body with each move. It exudes a resilient beauty born of rebirth through destruction.
-The stained glasses that form the Vitreum Dancers are varied and unique, making each Vitreum Dancer a unique existence.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình người, cơ thể được ghép từ những mảnh kính màu vỡ vụn. Ánh sáng lấp lánh tỏa ra từ thân thể nó mỗi khi di chuyển. Nó toát lên vẻ đẹp kiên cường, tái sinh từ sự hủy diệt.
+Những mảnh kính tạo nên Vitreum Dancer đều khác biệt và độc nhất, khiến mỗi cá thể trở thành một thực thể riêng biệt.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29558,10 +29558,10 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade and extraordinary might existing only in legends.
-Said to be the lost souls of fallen heroes, it was once witnessed slaying other Tacet Discords to protect villagers. Yet such acts were driven purely by an instinctual hunger for battle.
-Though it has lost its heart, it stubbornly clings to the vestiges of past honor, wandering the world in solitary defiance.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình người, khoác lên mình bộ lễ phục tinh tế, vung lưỡi kiếm sắc bén và sức mạnh phi thường chỉ có trong truyền thuyết.
+Tương truyền đó là linh hồn của những anh hùng đã ngã xuống, từng được chứng kiến đang tiêu diệt các Tacet Discord khác để bảo vệ dân làng. Nhưng những hành động ấy chỉ xuất phát từ bản năng thèm khát chiến đấu.
+Dù đã mất đi trái tim, nó vẫn ngoan cố bám víu vào những tàn tích danh dự xưa cũ, lang thang khắp thế gian trong sự phản kháng cô độc.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29631,12 +29631,13 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Gehinom gây Fusion DMG bằng 4% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh.
-Khi Gehinom tấn công mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#9a9da3&gt;A dragon-like Tacet Discord that haunts the peak of Penitent's End for an unknown reason, devouring all frequencies indiscriminately. Twisted by the frequencies of decay and death it consumes, it now appears as a dreadful, skeletal beast.
-Once a sacred place, this island is now a grave of sorrow, and anyone who comes for redemption must face its fire of judgment.
-Such is Gehinom, the Dragon of Dirge, whose flames burn to the bone, whose pain echoes, yearning for a final release.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Gehinom gây Sát Thương Fusion bằng 4% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh.
+Khi Gehinom tấn công mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình rồng lang thang trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số không phân biệt.
+Bị vặn xoắn bởi những tần số của sự mục nát và cái chết mà nó hấp thụ, giờ đây nó hiện ra như một con thú xương khủng khiếp.
+Từng là nơi linh thiêng, hòn đảo này giờ là nấm mồ của đau thương, và bất cứ ai đến để chuộc tội đều phải đối mặt với ngọn lửa phán xét của nó.
+Đó chính là Gehinom, Rồng Than Khóc, ngọn lửa của nó thiêu đốt đến tận xương tủy, nỗi đau vang vọng, khao khát một sự giải thoát cuối cùng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29703,9 +29704,9 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Galecrest Gladiators follow the will of freedom. Bound by neither rule nor glory, they become the blade that severs all chains.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Những chiến binh Septimont chiến đấu không giới hạn, kề vai sát cánh cùng Echo, luôn truy tìm sức mạnh đích thực.
+Chiến binh Gió Tự Do đi theo ý chí tự do. Không bị ràng buộc bởi luật lệ hay vinh quang, họ trở thành lưỡi kiếm chặt đứt mọi xiềng xích.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29772,9 +29773,9 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A stone statue TD that embodies deconstruction and reconstruction. Though sluggish and clumsy, its punches are devastating.
-It hurls rocks and other rock-mimic Tacet Discords as a means of attack.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một TD tượng đá đại diện cho sự hủy diệt và tái tạo. Dù di chuyển chậm chạp và vụng về, cú đấm của nó lại vô cùng tàn khốc.
+Nó ném đá và các Tacet Discord bắt chước đá khác để tấn công.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29842,10 +29843,10 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade. Seen only in the pale glow of the moon.
-Said to be the lingering shadows of heroes in the old days, their kind retains a chivalrous demeanor even as they decay into TDs.
-Glorious knights who have long forgotten their titles. Protectors with nothing to defend, bound by their relentless obsession with honor.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình người, khoác bộ lễ phục tinh xảo, vung lưỡi kiếm sắc bén. Chúng chỉ xuất hiện dưới ánh trăng mờ ảo.
+Tương truyền là những bóng ma còn vương vấn của các anh hùng ngày xưa, dù đã hóa thành TD, chúng vẫn giữ phong thái hiệp sĩ.
+Những chiến binh vinh quang đã lãng quên danh hiệu của mình. Những người bảo vệ chẳng còn gì để bảo vệ, chỉ còn lại nỗi ám ảnh dai dẳng về danh dự.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29912,9 +29913,9 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Lumiscale Constructs are composed of Jué's defensive modules, commonly known as "Loong's Scales."
-Họ are found throughout the Court of Savantae ruins in Mt. Firmament, tasked with eliminating intruders and potential threats to Jué.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Cấu trúc Vảy Ánh Sáng được tạo thành từ các mô-đun phòng thủ của Jué, thường được gọi là "Vảy Rồng".
+Chúng xuất hiện khắp nơi trong tàn tích Court of Savantae trên núi Firmament, với nhiệm vụ tiêu diệt kẻ xâm nhập và mối đe dọa tiềm tàng đối với Jué.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29984,12 +29985,12 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Khi bị Spectro Frazzle, Lorelei chịu thêm 100% sát thương.
-Mỗi khi Lorelei đánh trúng mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#9a9da3&gt;Once a remnant creature in Nimbus Sanctum, Lorelei gained intelligence through Sentinel Imperator's power, entrusted to purify corrupted frequencies drifting in the clouds.
-Yet wicked desires have transformed her into the "Queen of the Night," seeking to cloak the Sanctum in endless darkness to clear all sins.
-With her final grasp on reason, Lorelei sealed herself within the atrium, where she sings a haunting lament, awaiting one who can awaken her from this dismal slumber.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Dark&gt;DMG Havoc&lt;/color&gt;.
+Khi bị Spectro Frazzle, Lorelei chịu thêm 100% DMG.
+Mỗi khi Lorelei đánh trúng mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#9a9da3&gt;Từng là một sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã có được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao nhiệm vụ thanh lọc những tần số bị tha hóa trôi dạt trên mây.
+Nhưng dục vọng đen tối đã biến nàng thành "Nữ Hoàng Bóng Đêm", khao khát che phủ Sanctum trong bóng tối vĩnh cửu để xóa sạch mọi tội lỗi.
+Với chút lý trí cuối cùng, Lorelei đã tự giam mình trong đại sảnh, nơi nàng cất lên khúc bi ca ám ảnh, chờ đợi ai đó có thể đánh thức mình khỏi giấc ngủ u tối này.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30056,9 +30057,9 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Flamecrest Gladiators embody a warrior's undying passion. Wounds become fire, hardship their forge. Battle after battle, they chase a blood-lit path to their truest form.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Những đấu sĩ của Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn theo đuổi sức mạnh.
+Flamecrest Gladiators mang trong mình ngọn lửa đam mê bất diệt của chiến binh. Vết thương hóa thành lửa, gian khổ là lò rèn. Trận chiến nối tiếp trận chiến, họ theo đuổi con đường thấm đẫm máu để tìm về hình hài chân thật nhất.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30126,10 +30127,10 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A humanoid Tacet Discord clad in fine attire, wielding a sharp blade. Seen only in the radiance of the sun.
-Said to be the lost souls of fallen heroes, it retains an air of commanding dignity, even as a Tacet Discord.
-Once a knight who has long forgotten the title they once bore, it has lost all it was sworn to protect. Now, only an unyielding obsession with honor remains.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình người, khoác bộ lễ phục tinh xảo, vung lưỡi kiếm sắc bén. Chúng chỉ xuất hiện dưới ánh mặt trời rực rỡ.
+Tương truyền là linh hồn lạc lõng của những anh hùng đã ngã xuống, dù hóa thành Tacet Discord, chúng vẫn toát lên vẻ uy nghiêm của bậc thống lĩnh.
+Từng là một hiệp sĩ đã quên mất danh hiệu mình từng mang, chúng đã mất tất cả những gì từng thề bảo vệ. Giờ đây, chỉ còn lại nỗi ám ảnh không thể buông bỏ về danh dự.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30196,9 +30197,9 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;An enormous feline-mimic TD, only sighted in Mt. Firmament in Huanglong.
-According to the Hongzhen Chronicle, it is a solitary TD with four claws and a scaly back. It is called "Lightcrusher" because of the glowing tracks left in its wake.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một TD bắt chước loài mèo khổng lồ, chỉ được phát hiện tại Mt. Firmament ở Huanglong.
+Theo Hồng Chân Lục, đây là một TD đơn độc với bốn móng vuốt và lưng phủ vảy. Nó được gọi là "Lightcrusher" vì những vệt sáng rực rỡ để lại trên đường đi.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30266,10 +30267,10 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Kerasaurs are amphibious Tacet Discords mimicking Saurosuchus. Fierce in battles, they are named for the rows of horns covering their bodies.
-Not native to Septimont, Kerasaurs were introduced as gladiatorial opponents in matches, prized for their distinct appearance and aggressive behavior.
-Their pronounced territorial instincts also make them suitable for training as functional Echoes, where they serve in roles such as city defense and patrol.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Kerasaurs là những Tacet Discord lưỡng cư bắt chước loài Saurosuchus. Hung dữ trong chiến đấu, chúng được đặt tên theo hàng sừng phủ kín cơ thể.
+Không phải loài bản địa của Septimont, Kerasaurs được đưa vào làm đối thủ trong các trận đấu vì ngoại hình độc đáo và tính hung hãn.
+Bản năng lãnh thổ mạnh mẽ cũng khiến chúng phù hợp để huấn luyện thành Echo chức năng, phục vụ trong các vai trò như phòng thủ thành phố và tuần tra.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30340,13 +30341,13 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Khi Arsinosa tấn công mục tiêu, STA của mục tiêu sẽ giảm 100%, hiệu ứng kích hoạt mỗi 10 giây.
-Khi bước vào trận chiến, Arsinosa nhận được Shield tương đương 20% HP tối đa của cô. Nếu không chịu sát thương trong hơn 10 giây, cô sẽ nhận thêm Shield tương đương 20% HP tối đa.
-Khi Arsinosa tấn công mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, hiệu ứng kích hoạt mỗi 5 giây.
-&lt;color=#9a9da3&gt;Cô ấy guards the City of Glory, a valiant lioness of the arena.
-Built with the pristine white stones that Gryphons are carved out of and tempered in the echoes of battle cries and the laughter of heroes.
-This is Arsinosa, ever steadfast, watching over Septimont’s glory for all time.&lt;/color&gt;</t>
+Khi bước vào trận chiến, Arsinosa nhận được Khiên tương đương 20% HP tối đa của cô. Nếu không chịu DMG trong hơn 10 giây, cô sẽ nhận thêm Khiên tương đương 20% HP tối đa.
+Khi Arsinosa tấn công mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, hiệu ứng kích hoạt mỗi 5 giây.
+&lt;color=#9a9da3&gt;Nàng là người bảo vệ Thành Phố Vinh Quang, một sư tử cái dũng mãnh của đấu trường.
+Được đẽo từ những viên đá trắng tinh khiết dùng để tạc tượng Gryphon, tôi luyện trong tiếng vang chiến trận và nụ cười của những anh hùng.
+Đây là Arsinosa, luôn kiên định, canh giữ vinh quang của Septimont mãi mãi.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30415,11 +30416,11 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Khi Lampylumen Myriad gây sát thương, nó sẽ áp đặt 3 tầng hiệu ứng Glacio Chafe lên mục tiêu, kích hoạt mỗi 6 giây.
-&lt;color=#9a9da3&gt;An ensnarer that slumbers in a freezing mine pit, obsessed with collecting and imitating sounds. It can imitate human speech through a vibrating hum.
- Lampylumen Myriad uses sound as bait to lure its prey, which will be frozen in the deep cold. The loss of warmth and the illusion before dying will cause human beings to pour out their last words, which contain great emotional fluctuations.
- For Lampylumen Myriad, this is the frequency of the supreme taste.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Khi Lampylumen Myriad gây DMG, nó sẽ áp đặt 3 tầng hiệu ứng Glacio Chafe lên mục tiêu, kích hoạt mỗi 6 giây.
+&lt;color=#9a9da3&gt;Một kẻ phục kích ngủ quên trong hầm mỏ băng giá, ám ảnh với việc thu thập và bắt chước âm thanh. Nó có thể bắt chước giọng nói con người qua tiếng rung vo ve.
+Lampylumen Myriad dùng âm thanh làm mồi nhử con mồi, rồi đóng băng chúng trong cái lạnh thấu xương. Sự mất đi hơi ấm và ảo giác trước khi chết khiến con người thốt ra những lời cuối cùng chứa đầy cảm xúc mãnh liệt.
+Với Lampylumen Myriad, đây chính là tần số của hương vị tuyệt hảo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30486,9 +30487,9 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Lightcrest Gladiators uphold the ideal of justice. Họ bow to no tyrant, yield to no shadow. If justice has rotted, they shall forge it anew in light.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Những chiến binh Septimont chiến đấu không giới hạn, kề vai sát cánh cùng Echo, luôn truy tìm sức mạnh đích thực.
+Chiến binh Ánh Sáng kiên định với lý tưởng công lý. Không cúi đầu trước bạo chúa, không khuất phục trước bóng tối. Nếu công lý đã mục rữa, họ sẽ rèn lại nó trong ánh sáng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30555,9 +30556,9 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Frostcrest Gladiators bear unyielding resolve. Their fortitude is impervious to frost and bitter cold. Though blades may shatter, their creed endures.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Những chiến binh Septimont không bị ràng buộc, chiến đấu bên cạnh Echo, luôn truy tìm kẻ mạnh.
+Gladiator Sương Giá mang trong mình ý chí bất khuất. Sức chịu đựng của họ không gì lay chuyển trước băng giá hay cái lạnh thấu xương. Dù lưỡi kiếm có gãy, tín điều của họ vẫn trường tồn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30627,12 +30628,12 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Tấn công phản đòn Kelpie sẽ làm giảm thêm 50% Concerto Vibrancy của nó.
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+Tấn công phản đòn Kelpie sẽ làm giảm thêm 50% Sức Mạnh Rung Động của nó.
 Khi Kelpie không bị Hóa Đá, toàn bộ Kháng thuộc tính của nó tăng 200%.
-Khi Kelpie tấn công mục tiêu, Cooldown chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
-&lt;color=#9a9da3&gt;A humanoid TD born from the deep sea. Commonly found in all types of waters, it's known for its aggression and ferocity.
-It attacks with sharp claws laced with paralytic toxins, then rips its prey apart and swallows them whole.&lt;/color&gt;</t>
+Khi Kelpie tấn công mục tiêu, thời gian hồi chiêu của Resonance Skill và Resonance Liberation của mục tiêu sẽ bị kéo dài thêm 5 giây, kích hoạt mỗi 5 giây một lần.
+&lt;color=#9a9da3&gt;Một Tacet Discord hình người sinh ra từ biển sâu. Thường xuất hiện ở mọi loại vùng nước, nổi tiếng với sự hung hãn và tàn bạo.
+Nó tấn công bằng móng vuốt sắc bén tẩm độc gây tê liệt, rồi xé xác con mồi và nuốt chửng toàn bộ.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30698,8 +30699,8 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;A ferocious bear-mimic TD with Tacetite spikes on its head, neck, and shoulders. Its swings strike like a hurricane.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Một Tacet Discord bắt chước loài gấu hung dữ, với những gai Tacetite nhọn trên đầu, cổ và vai. Những cú vung tay của nó mạnh như bão tố.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30766,9 +30767,9 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;Gladiators of Septimont who fight unrestrictedly, side by side with Echoes, ever in pursuit of the strong.
-Thundercrest Gladiators wield stormborne might. Unmoved by favor and unbowed by power. Beneath the thunder’s judgment, right and wrong divide.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Những chiến binh Septimont chiến đấu không giới hạn, kề vai sát cánh cùng Echo, luôn truy tìm sức mạnh đích thực.
+Chiến binh Sấm Sét vận dụng sức mạnh của bão tố. Không bị lung lay bởi ân huệ, không cúi đầu trước quyền lực. Dưới sự phán xét của sấm sét, đúng sai phân minh.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30835,9 +30836,9 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-&lt;color=#9a9da3&gt;It holds the authority to command other Echoes of the Order, carrying out the Order's will to eliminate any transgressors.
-Just as the Order's authority is inviolable, so too is the power of the Echo.&lt;/color&gt;</t>
+          <t>Kẻ địch có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.
+&lt;color=#9a9da3&gt;Nó nắm quyền điều khiển các Echo khác trong Hội, thực thi ý chí của Hội để tiêu diệt mọi kẻ phản bội.
+Quyền uy của Hội là bất khả xâm phạm, và sức mạnh của Echo cũng vậy.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30903,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Cấp Độ Glory Mục Tiêu</t>
+          <t>Cấp Độ Vinh Quang Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -30968,8 +30969,8 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Rương Chiến Tích Ngọn Cờ: Đánh bại kẻ địch trong thử thách Banner of Conquest: Trung và Banner of Conquest: Major trong khu vực để nhận phần thưởng giá trị.
-Rương Chiến Tích Exploration: Những chiếc rương này nằm rải rác khắp khu vực. Sau khi kích hoạt các ngọn cờ trong thử thách, bạn có thể tận dụng sức mạnh của chúng để xác định vị trí rương. Chúng sẽ vẫn còn ở lại khu vực sau khi sự kiện kết thúc.</t>
+          <t>Rương Chiến Tích Ngọn Cờ: Đánh bại kẻ địch trong thử thách Ngọn Cờ Chinh Phục: Trung và Ngọn Cờ Chinh Phục: Cao trong khu vực để nhận phần thưởng giá trị.
+Rương Chiến Tích Thám Hiểm: Những chiếc rương này nằm rải rác khắp khu vực. Sau khi kích hoạt các ngọn cờ trong thử thách, bạn có thể tận dụng sức mạnh của chúng để xác định vị trí rương. Chúng sẽ vẫn còn ở lại khu vực sau khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
@@ -31036,8 +31037,8 @@
       <c r="M444" t="inlineStr">
         <is>
           <t>[
-Phúc Lành của Sư Tử Glory]:
-Những chiến binh vượt qua thử thách sẽ được Sư Tử Glory ban phúc: Tất cả Resonators trong đội tăng &lt;color=Highlight&gt;Fusion DMG&lt;/color&gt; Tấn Công, HP tối đa và &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+Phúc Lành của Sư Tử Vinh Quang]:
+Những chiến binh vượt qua thử thách sẽ được Sư Tử Vinh Quang ban phúc: Tất cả Resonator trong đội tăng &lt;color=Highlight&gt;25%&lt;/color&gt; ATK, HP tối đa và &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31168,8 +31169,8 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Rương Chiến Tích Ngọn Cờ: Đánh bại kẻ địch trong thử thách Banner of Conquest: Trung và Banner of Conquest: Major trong khu vực để nhận phần thưởng giá trị.
-Rương Chiến Tích Exploration: Những chiếc rương này nằm rải rác khắp khu vực. Sau khi kích hoạt các ngọn cờ trong thử thách, bạn có thể tận dụng sức mạnh của chúng để xác định vị trí rương. Chúng sẽ vẫn còn ở lại khu vực sau khi sự kiện kết thúc.</t>
+          <t>Rương Chiến Tích Ngọn Cờ: Đánh bại kẻ địch trong thử thách Ngọn Cờ Chinh Phục: Trung và Ngọn Cờ Chinh Phục: Cao trong khu vực để nhận phần thưởng giá trị.
+Rương Chiến Tích Thám Hiểm: Những chiếc rương này nằm rải rác khắp khu vực. Sau khi kích hoạt các ngọn cờ trong thử thách, bạn có thể tận dụng sức mạnh của chúng để xác định vị trí rương. Chúng sẽ vẫn còn ở lại khu vực sau khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
@@ -31234,7 +31235,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Giảm {0} Cooldown chiêu Resonance Skill.</t>
+          <t>Giảm {0} Thời gian hồi chiêu Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -31299,7 +31300,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Increase số Dream Fragments ban đầu lên {0}.</t>
+          <t>Tăng số Mảnh Giấc Mơ ban đầu lên {0}.</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31365,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ phục hồi {0} HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 3 giây một lần.</t>
+          <t>Né tránh thành công sẽ phục hồi {0} HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -31429,7 +31430,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội ban đầu lên {0}.</t>
+          <t>Tăng Cấp Đội ban đầu lên {0}.</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31495,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Increase số lượng Film Cuộn khởi đầu tối đa lên {0}</t>
+          <t>Tăng số lượng Phim Cuộn khởi đầu tối đa lên {0}</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31560,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Increase lượng Dream Fragment nhận được thêm {0}.</t>
+          <t>Tăng lượng Dream Fragment nhận được thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -31624,7 +31625,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm {0}, phần vượt mức sẽ chuyển thành Crit. DMG.</t>
+          <t>Tăng Crit. Rate thêm {0}, phần vượt mức sẽ chuyển thành Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -31689,7 +31690,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Increase tỷ lệ kích hoạt Đồng Điệu Cực Đại thêm {0}.</t>
+          <t>Tăng tỷ lệ kích hoạt Đồng Điệu Cực Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -31754,7 +31755,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Giảm DMG nhận vào {0}.</t>
+          <t>Giảm {0} DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -31819,7 +31820,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Increase số lượng Film Cuộn khởi đầu tối đa lên {0}</t>
+          <t>Tăng số lượng Phim Cuộn khởi đầu tối đa lên {0}</t>
         </is>
       </c>
     </row>
@@ -31884,7 +31885,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội ban đầu lên {0}.</t>
+          <t>Tăng Cấp Đội ban đầu lên {0}.</t>
         </is>
       </c>
     </row>
@@ -31949,7 +31950,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32015,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32079,7 +32080,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32144,7 +32145,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32210,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32275,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm {0} trong Lễ Hội Film Solaris.</t>
+          <t>Tăng ATK thêm {0} trong Lễ Hội Phim Solaris.</t>
         </is>
       </c>
     </row>
@@ -32339,7 +32340,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0} trong Solaris Film Festival.</t>
+          <t>Tăng HP thêm {0} trong Solaris Film Festival.</t>
         </is>
       </c>
     </row>
@@ -32404,7 +32405,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0} trong Solaris Film Festival.</t>
+          <t>Tăng HP thêm {0} trong Solaris Film Festival.</t>
         </is>
       </c>
     </row>
@@ -32469,7 +32470,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0} trong Solaris Film Festival.</t>
+          <t>Tăng HP thêm {0} trong Solaris Film Festival.</t>
         </is>
       </c>
     </row>
@@ -32534,7 +32535,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0} trong Solaris Film Festival.</t>
+          <t>Tăng HP thêm {0} trong Solaris Film Festival.</t>
         </is>
       </c>
     </row>
@@ -32599,7 +32600,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0} trong Solaris Film Festival.</t>
+          <t>Tăng HP thêm {0} trong Solaris Film Festival.</t>
         </is>
       </c>
     </row>
@@ -32729,7 +32730,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Mỗi Ngày Một Ly Tea Cẩu Kỷ [Tăng HP]</t>
+          <t>Mỗi Ngày Một Ly Trà Cẩu Kỷ [Tăng HP]</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32795,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Restore 40 Cuộn Film</t>
+          <t>Hồi phục 40 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -32859,7 +32860,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Restore lượng lớn Cuộn Film và HP</t>
+          <t>Hồi phục lượng lớn Cuộn Phim và HP</t>
         </is>
       </c>
     </row>
@@ -32924,7 +32925,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Dùng 8 Cuộn Film để tăng Cấp Đội thêm 1.</t>
+          <t>Dùng 8 Cuộn Phim để tăng Cấp Đội thêm 1.</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32990,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -33054,7 +33055,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Giảm tối đa Cuộn Film đi 10 để nhận 200 Dream Fragments</t>
+          <t>Giảm tối đa Cuộn Phim đi 10 để nhận 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -33119,7 +33120,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Giảm 10 Cuộn Film tối đa để tăng Cấp Đội 5-8.</t>
+          <t>Giảm 10 Cuộn Phim tối đa để tăng Cấp Đội 5-8.</t>
         </is>
       </c>
     </row>
@@ -33184,7 +33185,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Giảm tối đa Cuộn Film đi 10 để hồi phục 40 Cuộn Film</t>
+          <t>Giảm tối đa Cuộn Phim đi 10 để hồi phục 40 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33250,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Dùng 160 Dream Fragments để tăng Cấp Đội lên 5.</t>
+          <t>Dùng 160 Mảnh Giấc Mơ để tăng Cấp Đội lên 5.</t>
         </is>
       </c>
     </row>
@@ -33379,7 +33380,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội lên 3.</t>
+          <t>Tăng Cấp Đội lên 3.</t>
         </is>
       </c>
     </row>
@@ -33444,7 +33445,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Chiến thắng trận chiến khó để khôi phục 12 Cuộn Film và nhận 100 Dream Fragments</t>
+          <t>Chiến thắng trận chiến khó để khôi phục 12 Cuộn Phim và nhận 100 Mảnh Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -33509,7 +33510,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Dùng 4 Cuộn Film để trả lời và tăng Cấp Đội lên 5-8</t>
+          <t>Dùng 4 Cuộn Phim để trả lời và tăng Cấp Đội lên 5-8</t>
         </is>
       </c>
     </row>
@@ -33639,7 +33640,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dùng 160 Dream Fragments để hồi phục 24 Cuộn Film</t>
+          <t>Dùng 160 Mảnh Giấc Mơ để hồi phục 24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -33704,7 +33705,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -33769,7 +33770,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Win the battle để tăng Cấp Đội lên 3</t>
+          <t>Chiến thắng trận đấu để tăng Cấp Đội lên 3</t>
         </is>
       </c>
     </row>
@@ -33834,7 +33835,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -33964,7 +33965,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Increase số lượng Film Cuộn tối đa lên 30 hoặc 60</t>
+          <t>Tăng số lượng Phim Cuộn tối đa lên 30 hoặc 60</t>
         </is>
       </c>
     </row>
@@ -34094,7 +34095,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Giảm 10 Cuộn Film tối đa để tăng Cấp Đội 3-5.</t>
+          <t>Giảm 10 Cuộn Phim tối đa để tăng Cấp Đội 3-5.</t>
         </is>
       </c>
     </row>
@@ -34159,7 +34160,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Restore 24 Cuộn Film</t>
+          <t>Hồi phục 24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -34224,7 +34225,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Increase số lượng Film Cuộn tối đa lên 30</t>
+          <t>Tăng số lượng Phim Cuộn tối đa lên 30</t>
         </is>
       </c>
     </row>
@@ -34354,7 +34355,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 10%</t>
+          <t>Tăng Crit. DMG thêm 10%</t>
         </is>
       </c>
     </row>
@@ -34419,7 +34420,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Increase HP tối đa thêm 10%.</t>
+          <t>Tăng HP tối đa thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -34484,7 +34485,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Giảm 20% HP tối đa nhưng tăng 20% Tấn Công.</t>
+          <t>Giảm 20% HP tối đa nhưng tăng 20% ATK.</t>
         </is>
       </c>
     </row>
@@ -34549,7 +34550,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34615,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Restore một ít HP</t>
+          <t>Hồi phục một ít HP</t>
         </is>
       </c>
     </row>
@@ -34679,7 +34680,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film và chuẩn bị rời đi</t>
+          <t>Hồi phục 12 Cuộn Phim và chuẩn bị rời đi</t>
         </is>
       </c>
     </row>
@@ -34744,7 +34745,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Dùng 4 Cuộn Film để tăng Cấp Đội lên 1</t>
+          <t>Dùng 4 Cuộn Phim để tăng Cấp Đội lên 1</t>
         </is>
       </c>
     </row>
